--- a/dataset/kobert_ner_all.xlsx
+++ b/dataset/kobert_ner_all.xlsx
@@ -19,789 +19,936 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="261">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="310">
+  <x:si>
+    <x:t>노장 "5용 역양정보 지불강로 m3 폭탤O] 교) '내용량 D0965 349 쓰.Dp 190 kcal 15959 [질; 7요</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 " 땅 0 만:이 2업 '임8률 we 그소사 Vo CO ' dos 버터팅 버터랑 IIO J소0 벼-'키 땅콩 드 (639 땅콩 고소간 GU 버터g3드 30 '땅콩심 5O '2말 지단과자 7다 매타지자 마자 메타자자 용 퍽 '0VO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135242_jpg.rf.abb252704b88baf3364a050961d24d48_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135247_jpg.rf.cb8d38858c55f7bbc768a1513c8f0f9f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135235_jpg.rf.935465443d250aaedf5733a2169b9291_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135233_jpg.rf.b925baa0edf62342e9bf8e87118ab73f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>162 9 남약 매주시 coN 밀 인 애 d 엿땅 98.7 % 청제소금식물 마 [원재료명크림액 부 도덤 수소암모는 데 (설탕 제 트 따안유 스 미 k 건_ 보관방법 대로 671 수대 '반 터 보관시 시 도 이 접실 (위#' 사 대 의기 이 (망 p' 이 ^ 내용량 고구마형기지 [과사(유탕처리제품) 제며명 경기도 (주)코스모스제과 (식품뉴영 960번길다 금강로 진접움 (옆하다 CSmnS (http llwWW 후면표기일까지 '판울래 캐나다)] 소비기한 '가루[밀(미국 '유표올레인유(말레이시야산)| 토코메물(혼합형)] 당류가공품 콩비터(인도네시야신 [명 Potmto 스타 '글리세라지방산에 물 '생어노로로제 '양파액기스CM 코고아블 스6; 말투 (간미 [뽑안 곳예 '바로 '리에터레(내 4113 11986033205148 OBo 국심상 치하 ? 실해 세a 구입지 주의시입 선쥐 기다 (기뻐 통</x:t>
+  </x:si>
+  <x:si>
+    <x:t>버터롬 CGDM 골 1p2 3 오 틀 [- 67 'Dultor @ 품 예 &gt; 월 # 때 7 |대 버터림 골드 1550 ( ' " j0 예란관자 r 열 ( 표# 몇 끝 예단지다 (올 캠 @ 탑 [ {다다 표 풀 V O 애응 @ { 틈 [ = ' 품 7 9G 표 품 96 물 Coes Ct</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03035 "료 (주산) 훌라t위 [절탕 혼합식용휴채종유호 @*로 교양산동) E]전관액국산 현내랜드산) 표코야분말 땅콩버 중로_p125 77 수 우재호주산 {미기라당워말레이지야찬_ 정제 도구하소 주심지오 밀가루 난백액 판스테야린유 @중"둑 530-리제소금 '기타가공품 유화제 정 스톱사 및 구입관 비타민B2 드니다 입유 HPC [런물조과 3 (하바라기유 유화제} 전문기공품 핑장제 유화서2 합료, 오자 우요n요 고기대무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대S Mg 장자지 나고번호 ji@ 문; 사주 주2공장 사소면 표륭로 "_로') 국 무리[러미터) 신도 {날?기다 시물무지 #콤플리 #e신동E WDVI 유다 171%) 당가고9 8 89599 일@깊수요심다 소__ 쥐-발 긍정하고30가Na다 0전어조개, 전물 3e 모램) 자틈입늄 국 또보가지 ; 불정 모불굽과물 S햇 _ 식움올 피하여 실로 보과 - 반물 켓 제즈입 '고프 a신터 (07O487-231 12 mII 8 B910 00 Gat DaE 소비 I OVu eVe 꼬리 DBL Owg0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Digey Diged 83 Uo3 Diget( 간 식문유성 바사( 새추원 '하사버민 오리온 점심 업 떠 매 남' 밀암시 심히/ '노/문 만때 소재사 원 (쥐오리온 서물시 평산 구 백범로 90다길_ [제기해로면"기원-지 [_명혹분(옥수수 호주산 백색 ,식물성유제금올렉인유 말려이 탑 시야건; 채중유 호주산) 닭강정소스 외국새미국산; 미국산 중국 )외국신(인도산 M, 사과농축최v액; 닮근 수S9 (축액; 발표식초] , 기분 둘다 (n시주엉드라이드치_무#배다 V38 떠 '국내산) , 닭고기 |분말(치증껏 인도네시야산; 부음참깨 밑 대투 도미도, 내우 합유 불리예트랜 (문목보고번호 무유 망점 오침이 게; 야) 리' 4 디어M 농 Y끼사 (토마드O적도마토 아미노산농추댁 중국산))}, 파인애들주스 치간맛 국내신}; 뒤고기 구운선일염 (국내산) . 뒤고가 '최고기 [4장새진 12018060302319 }5이 {새{다. 민족 , 5' '고축어 고기 2026 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유 UI Ou 709 대용량 D요 제품 명 샌드에이속 웃음크림 소기원 |불무_기인 지 유형 과재유처리지록 I 보고번로 회유 평유 I7 '대투보유 제 원 제 주 동물 매 리므 포장재집 쇼트망기공유재감스테이리 9820A8IO2ISS 375 유'미국신) '0 토코대지n히해 [밀기루멘미국신)) [레시린 ( 기타; gy 유회제; (올레오레진로주머래 재료명 귀(깜스테이린워만레이시야신)] _ !기타가공경] 기다가39? ! 우지 기공유지 들 a {마가린 : '기공유속램유그하다신_ '편스 테이린유= 곡류기공품] 곡류가공품2 소트Y3W '역시리83397 당리판오레인유 '연세우위원위국내산)] (호모주스문 프로테이제 (곤입식용유 '8 '정제소금 [지심로 { 콤합제제트 진구 기공버터; ( 쇠고기유유 (항료] 항료2 진주시 [ 도당 [미리식품주전묵L별자치도 [신도조전제) 호소제 [S비영다) (신도조절제2 2? 해태제과식품쥐 '한강대로 용신구 서S특변시 트 움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대두, 밀, 쇠고기, 닭고기, 토마토, 우유, 조개류(굴) 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|우유|대두|쇠고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 대두, 우유 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|달걀|우유|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-SOY|B-MILK|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|계란|우유|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|쇠고기|우유|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RABO Grlpeftur 하리보 자목 책리 100 ((310 R J 의세 1 메께지 1333 하업 썰리사 설기다 399 공지밥다 새개길 70 "21578 _ 더시F 어신 무바무신 제기 주드시관 구민 '심합로 엘어베리 엉입경보 UBfime 33 UB BMMII  (U법 내5;   IOmng 급수되다 B70 입위 답; 0 지붕 Og 가리 Vg Us 0g (BOTu GNA A OI 0s 0s "0016 탑 바입니 차8? 거거런드 n Com harlbo NWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UU F 셈 외28고 넷애 인5 없이 집$ [바비체터 소콜러껏 후 K#a부도로 어거드t시햇로 4흉y-버{ 기입까지 무고런오 {영양장보 V추ig lial 제기 치피 {경가트 직임 정주시 `구 _로l 뜨집 미로 {진; 주월 T유-팔출로움 전문유 발a로적= 톤출히 4 미실팀 T기 -무E비럽물_하-_형 망플리 핑: (h물-턱자 팀주-물 비출님신: 식- 표로문t '가공유자 봉 (방고 분말유_ 소르  단자훨신 사리- 기터호움 스_톱 미0 U스리훨신 플로등스 진경 빚 {37j5P7 0Z3" 청트 백 감유 담 대지터 구교; 팔발: 유뜨로 쇠끼 고사( [지하 사과v 비교교t 빨- 퓨문기오자월 신 흑p 대 HACCP 두중5하다양x8 보l Z 곳 피온 커회국 한고 타스템SO '리 DAIa EWNIs DD 오기다 '부드움] I전만 {의D쉬리( '있다 I6i '방고 생명" ImD [mmMmm 플리하 만리맛 [사훨 소비 식 정요제 '매기지하신 . '발히-@오 돌레다지훨진  기루"다 '일현세 년문 전배] 퇴지부유 | [캠어터리D-스리돌 신드조절계경 스물장우지다 "뱉버V-기" '출서린 '글리리지림산-스르 (농소무해 비 트스템 | 본림히자기번 '본텔적U스물성으자 내_놈-분말 ,돼짓  영리 제로 방로j품 퍼러스 _바로회직식화 [[입거등 스썹제제식물성유자 계 제릭국 'UiJsr '80TTT7: [다? 숨기  은 l신물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소무다 HPC 03f)395 듭 @ 괴롭트T::로로} 탈물로고동 l투잔출월플유네달랍등) na @부망 또균] 고 [출플로픽록유-바S롭l옮하로이_양무페 수 [수제호주선 해바라기유 팔스테아린유 3오본길 [말가루 단백대 전문가공품 기타가공품 하여 주십지오 (제소금 평창제 유화제2 항료 비타민B2 자 '요금두렉030 리 스본사 뜻 무입한 귀 B요라마 시고기대무 입원 7니다 유유 흥체적위로 당콩: 유화째 유화제] 정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오': 6 입sA0 HLal "땅콩샌드 가루고 버VP 2불입 ( V다 립하하| IVp] |54 R도VJg개 이미 ' 400 ' ' CROMI 심 0 'R9 오 8 V 5 ' 어스 8 소 e 예 2 @ ' 8 예로 '대 $ J 용 d 중연 오 손 3 망 2 9 군 개I % 틈 뜰 중 동 호 틀 돈 뿐 퍽 출 뿐 8 도 틀 옆 출 틈 품 터 # 3 원 틈 출 sG31 739 C '움 명 류 물 영 별 톤 품</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐디뱀내하항 50 "훨8 ll음로 무중입지올유화 /물t 구1 [유등런문 -대인 (주크리운제과 전북자빌자지도 군섭 서주무드주P공질 소비기인 후면 표기일까지 짙리 소비션 땅 물없 올리고당; '중아놈 -데? 항되복숨이 #감미되 현 신도조절제 _ 산동중질 고전행) 기타스용우-기 필중야 소 불중이용3 똑중아항 ; [지고기 복승하학 버리주스 유화재 달걀 호두 밀 햇밀 영콩 4 J물움움유 망6어고기 록말록지증-콤무양 [률이용고 [한P5고기 오정어 엇기루다_ 조식 신불피하영 온도 [그시설서 저조하고 있습니다: '드십시오 패보전해 주요고 봉후 가급적리 및 영업_ 물은 의만 피해보상 교환 및 반품 론사고객앉다히말 고객상담실 엎출품 {@주 @  표꿈 과랑 부정 운n직품 진고는 국번없이  O 내용립 50 01 160 kcall 27 2017048457793 품목보 고 '고등어고지의 표기 7도 소비다 담080-109 섭저지 '안속니다 26 2 움망점보 WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RESEALABLE OPENANDRESEALAT CLICKSTRIP Shiiies) S 59 영입청보 480 Kc3 스스의자) 내요딩 ID '비닐규 48g텅 가로시 요 쪽부_@ 톤듭@ mm OTHER 나주이다 FEIIO로 점정지문 대스리 프똑O다 5낌 한신심리트 } 기니무히 4405 호 미라 이루 '미로 {이규 향 #해 -하3 | 훨신지: 중국 출 푹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|쇠고기|우유|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|및|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유 및 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7 4 h진 무 너대 ; [활@ 2 "주려주스 중행 9 '유유하 잔 용 이 지온 '오. 제 70 오 'T 개용 곳대 보관해 모생 F ' [ 내기보상 바고 그_품신교 ( [명양청보 160 MI 7 I 낱p필 욕 문미 1339가) 유 계 "Vun s 7무보: 9a히) 설다 포기의 신망다 '맨 (소바기다 '올리고  "신도조실? 'ga안 '산도조질제 ` '"중 거i 보 k료 "복숨083 [감이회 : '복숨082 '물잘오다 '유 도모 '피하다 폐고기도 {조리국튼 5오 직량 살이다- ; 가_ 매_OL 시용산무 [제조하고 ' 자조시서 (주시고 '(서용979 은 '7 경식품 내끝니 377 KCI 새</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANUA) Gapnsaiyes} 터시 매596 내륙화 1000 연인정보 304 태시고기 IIO) T? TILY 0029 -:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>open 중 a 굶 i @ 낙 고 옆 사 '7 유 야 팩 7 출 모 탓 푹 못 # 무 흙 뼈 틈 초고y 품 조집 무기 Chd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시5 'Ue 에너지바 N 백런스 ULIHIIIII 대다꺼N지 Post 에너 교 에너 의부 0) IV mImm " 100 어39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오리근 '합입예속 ! 들어가는 미니사이즈 미니 나늄포장되어 보관 휴대가 가프 제품명 다이제 미니 식품유형 | 조홀[가공품 포장재질 | 플리프로필렌 업소명 뜻 소재지| R오리혼 제2의산공장 전물특별자치- 의산시 설동로 23길 기 원재울히 ] 밀가루 (말 미국산) , 다이제조국랫[백설탕 식물성유지말레이시야살) 전장 플유두질랜드산) '불고이큰말; 조로크럼] 식물-용지금유 말레이시야산; 팔플레인움 플라이시야산 백설탕 전립분 전지분유 오트-런지 잔드조증제 공종 말-사관 산 밀구츠 코크럼 후유 대도 학유 소비기한 | 즉면주기일까지 품목보고번호 [ 19760487005157 발품들 물루 특출이 통하듣- 팬집_기 최퓨- 품고- 옷며어 문해 # 조커로 꿀 발문함) 혼일가등 주퍼지 길국국에 인런 걱행 보활: -원 셋살홀컴출i해용 1399 가 낮르' 국데 보관 '개공루 가급증 뿌리 들서온 부정 반문치 본사 및 구입인 고객센터 {화) 080 '023-5700 (문자) 1522-4002 영양정보 중 내용밤 80 8(40 g X 2봉지) / 1롭지(40 인당 197 kcal 나르급 Z0) 10 % 민수화: 26 8 *| 남류 DDE 10 In요 17 % 랜스시밥 U, 무라지 고보 40 제밤 오;ng미만' % 나때 식 59 플레스레: "맨 생망하 7: a내 대욱 UA 7 (MM) (주오리c HACCD atTt '80 905 파이제 중 c dSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J론풍 E: 글느; I8 9r Z9 겨y C 터거 803보 09goo 268/C @기0I60U n리 IA 091 Grrg Ge 서구하4"38531 8스경= 269</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그회 어리거 S 느 P어 영0 보 UBV 600 268 088818 ' 기;이다 Smo O뇨 NS 0a 스지다 09 09 OmnO 57 uo 4653 VeoI UJizw OL 5332 Anlae Cad :어9s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥스다 K 09 이 mI [H 소 O 이 (O 6 거개  기) 25까지 2026, N리INa WN '제Iila GM 입소입 기인N 소새N Ved OOaliBokCa '(0EN 'io 109 없새요버 06 'Noll</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-SOY|B-WHEAT|O|O|O|B-MILK|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대두|밀|쇠고기|닭고기|토마토|우유|조개류(굴)|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-SOY|O|O|B-EGG|O|B-WHEAT|O|B-PEANUT|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(ARUBO) Ii " li "MI-S 하리보 프루티부시 두미주 이 바리보 아S 꼬다' 10D KCal) 메 개민 표사점 #이싸기 바가다 는 리 3중프리지 78 시 02-5/8-0385 17연신 "5 시대 V3 M입 끼0 Gerivo) W0O p 가꾸다 WOOI디 자고기 이터 '01340 '김기5 새꺼거 곤미입 '376(2 '리0 N햇 Doroso yorttoo WWW 닫;^</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|달걀|우유|대두|복숭아|돼지고기|쇠고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-MILK|B-SOY|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 대두, 우유, 땅콩, 달걀, 쇠고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>k'세곰 나의티타임 달린미 E입 소자 슈* 함께 튼튼안다 '위만 휴세 @hocl?3 CSOSOO m P리 [모집지심다리 UO무리 330 1각터 기소치루 대한 79표7 (사시1 서로 '신지분위-지나드썹) 오 히가긴 리 코선이버 신어 의' 아예 미계 피내부 느세요 장'" 메이트 커뻐; po트 '이침까지 요골 FZSU-ITI DS 영양장보 {식찮미 a하: 바가 Igt6Dsatoo'u7 신국보 고번소 ~"리산-김 식8생유시만다이시야신) 주오리 보수3보 쇠지 @ 신비서20 '그O베다 용 A l6o</x:t>
+  </x:si>
+  <x:si>
+    <x:t>린0 말리 기타 댁린 힘유 @로움점일행 한천 '힘유제 조건제어모제베진로생승 %) (8959% l출 다요시설사트 일일길숲 플발콤플해탓 @혼고등 국번 M개류물전부 홍합 또 보심 가능 부덤 및 l사관신올 피하여 실문 텅각 '제조권 G5 산도조질제] P고"' '536 스고 {감미료) 식용유지가]품 산도조절제? 되지고기루송야 복숨이능-액 당알코올 171 D 말리돌 '알코올말터늄액  있습니다 '고등어계점; , "ui자kdy 모람) 잔 신고 교다 CtA 묻람식문 3311 반조 '고개지경센터 (070)4637 2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@ 아도: 이리덕 @움 눈씨니 얼굴 #Q로 가꾸_a P  내gD Ii0 Io9 1당류022 U2pral 미0D시 08 TU 2DNC @_이멘로 runrorhoulCo Ld '수입원 신n로 'NA'</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-EGG|B-MILK|B-SOY|O|O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|대두|쇠고기|토마토|달걀|호두|밀|메밀|땅콩|고등어|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 달걀, 우유, 대두, 복숭아, 돼지고기, 쇠고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>인식 불가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O|O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tokens</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C' o0- 도 Blenc Cr 산도 깊은 '불런드 새빵 커미 내용 ;"요| 맨맨7 "Ay 이미국심 시답 사다 0 대무구 0 10 "0o답 왜7 소들기물 '"랜-그리{ 담기 비다 럽나위 '93 '언제 브대 나두유 무리다 방' 신문 '입82s ID 벤시터 42 고함 미 반물 시고기; 햇i 본사 책미 V '주터 리시오 덮 ` 진임음수 d9 구입런 소비자3 예 또보트이금보 0 의반 내 보심 신과 F메 (서3 V 버II VM TI 디y '가사T다이 31 Y다 8: TC 29 RUASTING  GOFH 풍미의 바섯 시그니처 '이미지예 (운산' FEI 기심;임 며자 나오 IDV3IG5I "심새생 소비기인 g리BaI지_P CPn Y새Lw [가이인 드움째 영양정보 유끼 소재새 '대인터 [선생요시 [민드마루다 (알레이시야신) ug:' 비R 신어서로 @소자덧 세O스 P 기비터리 예스내e (너_=국신)) 어징래 p재기끔 P외유 iCal 가,재; '기다기공히 {아H이N야신) 그) "중어제제스비다 "드바켓자 그다자' JAL 유자 , 산도츠 니 언드 'Q어스보 a 아스기보이지적 재심국기피므두 '해다F Rl요요 P리어스; '리싸리 FPA '모라리신6다 Rr s {어디오피야신 자; 대기가 유어자금다 '밑가  '-N3다 그거하다 '피의고 NSCTII 모시 53 V시  모아지대S '구u움이 '고재상미실: Wco? (수신사요주부 V7I TBUI UD' '년N)- IUP 8882</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 대두, 쇠고기, 토마토, 달걀, 호두, 밀, 메밀, 땅콩, 고등어 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Salmif Canoylngieo desloseau and iarnkmt  manos Sugar; 3neni dmount0 u % Podu Mah NTavill Erin 영입경보 659 U망 0g 소고기 OR SAVAA 바이 c 0o시 USO 스_쏘 'horibo WWWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CKOWN TI Sigran&amp; 도 RUlBIlRGCOIII 기으 끓미의 F 플 바x시니처 불런드 운산 C( 앞영 이미N에 너거린 219 8" 소I 소비기신 만기_끼기 엉양정보 NU N뇌 37 kcal 그스 커피 미(지t기이 "미 ""새" '리n '시다 '미7대 고기 미과 I09팀 가스L ATAIISI 소속 '증기 대무구 신@-T" "7 " 소끼시 {w리이지이신 ,미a 무 나SU IWmn M키만 마르다' 계자 ;재끗자품-a 자? UUI 고녀이시다신 'n)lt 6비 [n대 기터가리히 _가계 시미 d점9 틈 플_패손t # 어리오리야산 m0  무하자 언제 NUn 가미 어기뻐터 가모니지 'V2d ToI 다스지다하7 잎: 피지:2u 시교 입사 @ 7색   ? 고요두문  y인소 스모 구입나 FL신 휴 깨어고 9 나으; Be9 되-꽤어 왜 U UI 뇌' 신a 비리Oln) '인 어고하다 [라s '내 이다 IX II '거W) 쿠르다스 커피 Olend 3eA Ue 가괜리{ # -가 ITI ( 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134347_jpg.rf.baceb8a8302550ff7b5b772780f96d25_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134351_jpg.rf.e7f3169faaf7fb813f2beb1cafb5b28e_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134914_jpg.rf.7cee80a5db824002c096a87e82813a54_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134815_jpg.rf.67e5a1f020ef1497e57ca19281cf0a5b_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134837_jpg.rf.ed4d94df21a4396911884068a76f69cb_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134845_jpg.rf.8fde562ca1a108fa765b02fd8f8d47f4_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134906_jpg.rf.0ad513d152b43592df5b1a127986367a_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134736_jpg.rf.03a2493adcbaa0d016790bc19865b1ce_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134822_jpg.rf.6262b41eb47cd6c2a3822e89e46e4dd0_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134417_jpg.rf.6c87b434b730b69faf7c535b85711c38_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134713_jpg.rf.14f7b250dd0697ed26398ceec5e9e176_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134746_jpg.rf.7d1a7cd82aa48c73d4ec530cbdac8bcb_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134903_jpg.rf.3d5b95d8da7b6d2e8339eba1c797c43d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134851_jpg.rf.ac5b8260ed1b605528c81736dcdbbb49_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134849_jpg.rf.b34bfd20083649cde5b04fb36cb8010e_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134753_jpg.rf.15ac27dc4ca10f457820a91f4c092b6d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134825_jpg.rf.fc0da97da2e2f3ac418e3956ebbdbb9b_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134813_jpg.rf.517885023019c99bc7e7c403b8a1c62f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134117_jpg.rf.f9193e833be81b64775c29fcaa2cfd03_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134628_jpg.rf.8af5ece5fd8330cdc2d0d3faaabf1a03_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134806_jpg.rf.bbeca6756c7042e21136edfd37395545_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134026_jpg.rf.4c1217df5150fb504b6a4da92d90376d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134835_jpg.rf.5e6d47619c65a4ce05e7463f1a19ff67_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134727_jpg.rf.a578b1bf67f08e0aab4d7d5adafbb5a8_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134731_jpg.rf.2d9c0647831288fa80bdce9448caaef2_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134041_jpg.rf.03b9cf371e46c2eacede4e7f81371000_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134405_jpg.rf.95f755a58c8b6cf0b264befa51185eac_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50 5 제1  (국색스 Ne 밀 우유 대륙 [소비기화 |말런 또기히하집물표보고a IIYAMOe 포장재질|몰리프로필로내포장면 해태제과식품(주) / 천안2공장 (제 조원 |중법 천요스 지률- |울 n@호 [유통전문 올림언해대짚구 [길 기히하다 '용신구 컬리다 [판 매 원 및 '본 미벼 '38* #8 곳 *이 '생격 주 내내' '하안 7 k 소골되다 벌스가' 사사)  주 스틱 NKy {관틱 [제품명 [포키 극세식품유다 조골렉가공품 [원재료명 및 '당 코코아매스데덜관드산) 가공유제성가교로산  합량 | [밀가루밀호주산 소트님 떠gP 코코아버터; W? '미국신 Sv '정제소금. 유화제2 흔합제제치자황색소 유화제] '항금 8대터 산도조절제2 효모 호소제 정제수 프로미 하&amp; 이황산류 한강대로 서울특별시  충륭이 서늘히고 피하여 습기찬 곳을 '공성거대워원화  세물은 직사광선 ((KU ` '요금부럼 ( 주십시오 '수신자 보관하여 W '고객만족실: '국번없이 곳에 N3r 도미도] 피해보상 신고는 '세중온 '불랑식품 = (의거 힘으나 '있습니다 ` '부정' 구입한 '세조하고 보다하스 6677) ' #년송이 . 'U이하로 보사 및 I석예서 불하이터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135100_jpg.rf.3c23731905038a9416812b77b97ccd0d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135040_jpg.rf.f7da6981331cae8b1147ec22262c0299_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135255_jpg.rf.a253a54578c177d14a2c6f6b77537cf3_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135119_jpg.rf.5bea5b747bfcdbb33715b447d584fb8a_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135109_jpg.rf.a01a3efe927a2f61824a308f4037da14_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135027_jpg.rf.4ff42b17b0cedce17928bba7f99f5bc7_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135048_jpg.rf.e5ec8866244bcb886b65af1aa1d101a0_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135114_jpg.rf.2ae53fecca16efb69a021642a25d3344_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135201_jpg.rf.bc9bcbfca21f473348d843f6903690aa_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135147_jpg.rf.dea51915bf68e68753dbef52df8d0d18_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135144_jpg.rf.a86f09efef8dd4349d5ad8609c080c8c_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135025_jpg.rf.5c4003af9a67de40a7f7f5b7d38cbb16_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_135052_jpg.rf.fe84f3b2c209aa356c6375f55b5e47a4_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설탕, 포도당시럽, 팜유, 구연산, 덱스트린, 변성전분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|대두|우유|땅콩|달걀|쇠고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-WHEAT|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-MILK|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라pa;^ 소컷끼이 5I 가 IS 5 I AIil 98na4드새} Ooh 조미기 149 김수시하다? '오리온 (주공장 비림 주 스지 둘멋 학수 '3중 식S i집망고 '식물' 발들T스트레 음@ 말 구언산  "필말 대로 텅 구모저 해j 방움 흉업떼= 재후 개 1399 부정 "l 릭=트 평콩; 의한 불로기통 '책장 둘하올다 곳 본사말 '반문치' WI 망고리싸다? 구 { 1ena 8 SUI 어씨 8베5 경정보 I0m 가너U)기 모심재심 '식3청으치다 직출유교 | 밀리  사가" {립불/인요 효심복도 '밀리미시야산; '근래 소비담유 또도망 요거트분길, 0-소비물먹 물치로유 소르비단지방산-스크리 산도조전제 전끗 '예트님신 ; 문말유크림 #E미3 물린 상우지2 {방산계스템로 백설탕; 국N고기 '이스라결산 온함제제키변성전문 , 성문사 물리리지등 'S입제-3식물 (농춧무데' '꽂로필런리룹 '비져나농죽분등 행료제제방료 집입가등 '비라물태 Biiy HO '-카로켓칙색로 초료출 'Biim [0리비야켓 'z없이 (혼합제체식물성유자 9요 오징업 '불랑식품 닮고기 토미토 '피해보상 호두 '기본번에 "습도가 낮은 소비자 511253 - Ioym   c-등c장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|우유|대두|땅콩|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|대두|계란|우유|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기, 복숭아 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기|토마토|복숭아|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 밀, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>corrected_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quality_label</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|우유|대두|아황산류|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-SOY|B-MILK|B-PEANUT|B-EGG|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0 @ 1' ; 그_ 814973"6u 319 도 S찌문- h미다 oouinc 무 4Ol Ke) 소입스 4보 숙r_ ) 장유자3E 이디 유지유 비사스 표망사다 아리베이터 닭 96 IW '0J버7 On' F_E @ER보O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{ 출 환통 EIDSICal [원질보 IIV 틀 Vu 70 42 운안: - ; 7 { 틈 통 총 = 흙 = 총 [ 도 틀 OEH 출 비"g] u v';NA 터t:] 구 c6 " 부벼 V'a otovo 무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마켓오만니보기' urt87737하- #En# 건요법다 I 갖구위번듯 크러스트가살아있는 '이미지예 카페스타일 브라우니 더진해지고꾸덕해진 AIl New Browniel 브리우다 직품유리 조골릿가공품 소비기합 밑민 포기인까지 제물명 _미즈오 모장재질 문리프로밀런 [슬륭로하칙 @_자-임_지 서로오" 업소명 및 소새지 출요컵움 매음정퍼제V렉어지어퍼m전어유포물_신 l어다 l근; 푸어로히캐정말하국-음글량력 @ 야재물 진지로주포랑스신-멘표히로 코문아버터], 밀가루밀 미국신) 가공버터 '고보야분말 당류가공품 분 전텔액 갈색설다 기타설탕 매실탕 옥수수선분 백설탕 {가당연유 리업초고집 유크림 주정0 60 %| 내용량 240 gX I2개) 식염' 밀크로문크럼 , 요함제제탄산수소나트 [영양정보 1깨2 9 당 8 kaal 둘 산성피로인신나트급 , 쌀가루; 무마르산) , [일 영양성분 1009 담 (잔단경; 부수버터오일 항료 2종 [개 당 기준치예 대한비 6간 우유 대누 한문 40 mIg 2 % ig0 mg 10 % 호두 복숨이, 도마투 , 돼지고기 심 나트답 12 9 4 % 61 19 % '문류; 오4어 새우 개 ; 소개뒤(군 난수화념 8 % 41요4 술갑 모집) 손입가능 당류 8 9 39 제물의 친선 - 보론: 위대 진소로진 하멋 지밤 41 9 8 9 2 9 습니다 반문서 본사 및 구입럽 모랜스지밥 0.5 0 미만 05 9 미만 식사감선 ; 피해 온 넷' 국에 포회시밥 Y인 14 % I1g 79 * 모델 개본 부 기국석 빨리 드세:, 스Ha 1 "보 5 6 79 T 26 % 소비자 기난번에 의진 피해보심 2 9 6n고희 부심 김식움 신기 '밑없이 I301 Iu 소개센터 (선다) (MI 03-57U 떠마 : 기준지세 대다 Bcil 다) 무개 1572-Ay I냐dt: 개방 교 주3에 I 66 64 N J ' # 쇼 Ilf 'gD 닮고기; 주5기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소 평요 같온 시용한 불륭옷 임 '꿈유환 주면 개란 '접은 매내학운으엔' 필 매밀 투바물스권 보랜 기붕 [현a보보호 교환 : 'Dexnst C2: LaryN2 Nhi Ps반 리사묘 제소인' '청제소금 물프로편권 입종외' 식사 광선국 S수 S소히 가 내:당새) 실탕 섭-기5 시언어서- [인부로 문시일 당처리새품) '인구의 (원새금명 '제품과: '수입만대액 과재유 '검은색 새우물 @끼진 '갈색이다 오비기화 토미도 그반에이 ) 신고노 우유 불림식품</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아리보 드어린 여3,정다 세 M표8 일, 우유m '@안 제 기은 세조시 Y예서 메조히고 미l니다 J268 kcal) 라드 긍성거래히 언쥐 교사 모생대리 기본어 이거 표시적의 | 실꺼기 '면 맡T 수 ^ 3나 기 무껑 김 식8 신고' 겁가노 국두 하이 1399 제3 내 입쓰덩어리가 간국실 70 '권립 수 있으u 미는 제즈? 9예 검계수 서 사용다 식장터분이 군어&lt; 구업 으도 인사예 유해하니 제거 $ 바거로연 영입U보 u83 800 268) Ug급딩 |말 @입 청_ 기O내 다르 @수의요 627 고기 도이도 목숨이 입 에 지반 Oa 3UA 트대 N멘 0 모화시망 0 Omio '50 Ue [표 113055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50 5 제1 (국색스 Ne 밀 우유 대륙 [소비기화 |말런 또기히하집물표보고a IIYAMOe 포장재질|몰리프로필로내포장면 해태제과식품(주) / 천안2공장 (제 조원 |중법 천요스 지률- |울 n@호 [유통전문 올림언해대짚구 [길 기히하다 '용신구 컬리다 [판 매 원 및 '본 미벼 '38* #8 곳 *이 '생격 주 내내' '하안 7 k 소골되다 벌스가' 사사) 주 스틱 NKy {관틱 [제품명 [포키 극세식품유다 조골렉가공품 [원재료명 및 '당 코코아매스데덜관드산) 가공유제성가교로산 합량 | [밀가루밀호주산 소트님 떠gP 코코아버터; W? '미국신 Sv '정제소금. 유화제2 흔합제제치자황색소 유화제] '항금 8대터 산도조절제2 효모 호소제 정제수 프로미 하&amp; 이황산류 한강대로 서울특별시 충륭이 서늘히고 피하여 습기찬 곳을 '공성거대워원화 세물은 직사광선 ((KU ` '요금부럼 ( 주십시오 '수신자 보관하여 W '고객만족실: '국번없이 곳에 N3r 도미도] 피해보상 신고는 '세중온 '불랑식품 = (의거 힘으나 '있습니다 ` '부정' 구입한 '세조하고 보다하스 6677) ' #년송이 . 'U이하로 보사 및 I석예서 불하이터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83 구끔자 깊심 산 코어마터 기에익 맘계 버비I k기 '바MZ요표미티진터 Ti다 U생 Da 주껍무서 "조키a 입기 2.160 ' g80 3 시이산 {가가라 Yer" '텍스데) 유1'오 '다기급R yy; Ln SIXITEIIRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>용세의 35버i생인 Gni 농빛 Orone 용 LOTT 1952 E내a내교레교 ESnP 퀴T [지발 재조판매인 '켓가필문 '선탕 코 늘틱 11m5 '유표움;가궁무자-거WE 국신) @대타유유 88 % 합심 남비 '구멍 심심 말 예반 03 % 곳예 진 무:  '깨내 보심 시한반 '반집이 생길 수 8 "801062' 및 #없이 녹아 히안 교민 유n 춤 '신고트 국 없이 }리늄 버문 미a '부점; 고문 마련 만 가능 유지 하 k입 제료 실이I IIUI 10o VO (영양정보 (10030306010121 {리프로-데 경기대로 진위면 '미국신 전멋 식도 법그럭 핑버시 #기인까지언 김기도 '11 920 k데랜무드(주) ` '코야분밥| 인기리밥 '딱스테다리R업 소비기 '곤함문유; (끝분변유 n유 그데스U다 R1미국신) , 소드님) (기공유지 '메y미로) 골렉기공유세싱가포고산 , 식즌유임 손입분유]  0-소비터 '?함식용유(경화유) { (정제수 합요끓} {전리객 {정비소금 손함분유유그레국내신 , {인재료임 (선탕; 가공유재싱가꾸른산) , 신M 쇼드님(기3유지; {유청단내분마 신5조 심제23, {유Y미 '기타선틱(실탕 전분) '기타코 코아가공품 플래인유) , '기타가공품 주정0  '본사계서 고남지원5터 유라세2중 변질감은 드시도 무대하다 '인헤예 '청류주0 있의u "8c26 의합 피배 '소비자기본번예 습기루 '식사관선 ' 1399 조|릿 붙람식협 '뻔심습니다: 돼지고기 { #]_자다 ZEC 야채 야채</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"II Mm @H UoRuvo (3 ZoVR 시우얘 U 새밥화 밑 우부 '시B반 제법 U5 까도하고 옛7니다 60 G?Bd C에) 문 제무은 관접 고시 년 몹시a 입까지바 VFORLO 연 (티길 0? 0-8363 굽시다 연양정보 uTa OMIV FN Nu 소고기 입유 bNI 원산지 Kurmi Comw harlbo; WWW 터키</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 9 COUU 1apan미 퍼지문지리_; 소비기래 이신 '리사리지밥산-- 수입 판대인 스배: 질로-품물주 료록집주_로립하문@ 도S 백신당-플옥주수전다; 플도 텍스트렉 포도관 '전진자현문 쫓대 물관 개품 후가금적 시E님 '피해보장 피해 및 구입간 미어 미합 399 문저: 본 스신수 국번없이 무전 '깨끗히  'o시젠트 보미는 2 듯 모 푹 쇼 ("우 'Rer OaIOMFODD 메주- 주오리2 그리세린사렉신예 [감치하테이크기(김자, 요소제 신도소럽제2 ~리리 E요 구연산]. '민길자맛분만 '실제소금 습뇨가 시O성크림 '직사찮신, 있습니대 안심히고 신고 이므로 , 굉팅식문 반심은 ZII 초23 편집 TK Chocrip 기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00 8  3 '어쨌리? 눈말 40 셋 233 (행점 '의한 유 힘 8 '7후리로L보 6 명 758 % ASI23tzgyligrg oTDDSU2 (생포로사 올리기유 조릿공품 '유화지 5린 학심 [가공유제경의유) 비E오다 17399. 냄저 '소비지기밥벌다 요이다 [명양정보 62876 '지도함위 LmPI '직장선및 y시고L Ia 내L꾸다 {보움 [물E 내용량 Doo피 EmDal Ey배Og 349 190 kcal I5q 'B0SX [`기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OOI Muamd Tryuliiors 09 Dpnilina Iarti Uonna 교4 poslor Oumulise( 4m wo) Wheat Soteawoylom dimiT SmnAS MikzNnavulloy 600Fax 2I2 ";어 거없0 UI '리가 미어 '다I 3 '대터니다 영양징보 098 BIO 입 ou oity K9 AyD' (Naiai]) ODa +90 구UU M 0 1.Xw O/vu 'n기 Gom 'horlbo WWW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VV VUU 이기'신) I0I2 미시7 [모강깨신 [ionyo'''oa12? 메미 안침 내기고기 고기 오집이 소개; 모양) 싶사인기다 눈생대 거교 나 보심계 있,니 반 " 물강소 수입시 넷 고개g다 플시적히실# - 화심터 고개상되다 080 '900-6133주 '뜨거;니 부다) dsajocoki 깨소신 예구 깨끗이 우리바늄 깨야 이사 UI) 부성 불림 시멘 신고는 국장 없이 1399) 새미이" 오다 | ?래인{m도리 UnMI 기래하인히 {불보사고넷; 우리지다 주이서:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133353_jpg.rf.5e6f59227143fff9dbf806cfac7fad26_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133608_jpg.rf.ce798d41b7948148205776e62f76ac1d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@S제8 2&gt; 6 o8 주R88 D3*uhf WfDbLAADf _발움 듣 DIDLiIZ bY드 IPJe S81 곁</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-MILK|B-SOY|B-PEANUT|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-SOY|B-EGG|B-MILK|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제품명 : 권더 조골핏 쿠리이이이 식품유형 : 준조클렉 이야기락 총 우유성분 : 3396. 충 코코야인로 1393 원재료명 : 밀크조골렉 4096 (설탕 전지분유 우리마이 0 코코아버터 코코아매스 레시린 향료 이어기만 (바닐린향)) , 설탕, 탈지분유 식물성지방 무수유지방 레시린 향료바닐리향) Oe 알레로기 정보:우유 대무 합유 제조원 Ferrero FoodlHangzhou) Co Lid QR코드스랜무 어플레이두다운로드 수입원 : 폐레로 아시야 리미티드 한국지점 STORY 이일랜드록선댁 (반물교환업무 소재지: 경기도 평택시 진위면 진위서로 63) 판매원 : 매일유업주) 경기도 우리아이외 함께다양한이야기블 평택시 진위면 진위서로 63 직사장선들 단들고 위고 또든어보세요 피해 건조하고 서늘한 곳에 보관 톤 제품은 그라-기 로야 코다; 스" 컴우 2시간 공정거래위원회 고시에 의거 고환 또는 보상 미다-기 이미데당 모이서새국_이야기념 받울 수 있습니다 부정: 불량식품 신고는 수입주L다 5PPO 느 이33053 업애 미미미심 수 국번없이 1399 고객상담실 : 1588-1559 하다 반품 및 교환 : 구입처 및 수입원 영양정보 내용량 509 284kcal 나르문 615rig 39이 | 탑수화물 2720 8%| 당류 26.79 2796  지방 1759 328 트랜스지방 029 포화지방 1139 759 콤레스템물 175mg 66 단백질스49 896 갈술 I5Omig 21% 인 1225ma 18*6 1 영입성분 기준기언 대한 비어찌은2@아m 기준이므로 개인의 밀교 입림에 미라 힘글니다 8017"7609 원신지; 중국 소비기합(입원년 까지) 옆면 표기 상상이 재f는</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직품유히 건다하| 내용히 509 그리l어저 %교운ml 부부백; 콤어 위요-문-흥l l _인 안생로 7길 ? [흉목보고로200V @ 3 소비기한 {우면 표기일까지 잘리린 0 [로궁l륭 물히 올리고등-사고동- 353 #섯리먹탄? 2 오도-철제, 산도조절제2 산도중적제? [졸- 불전적일하지겹다 }문유지강3요 롭_ 심장속소 청제수 시자항색소. 대두 땅공 흔입가능 '직사콤_물 피양여 호도  은 '중안 대두 요공 동록 '급적 불러듯집시용 그관 및 반문 본시고_상담실 및 신고논 야므l 신공호다 '번없이 1399 과랑 접심지 4 내설신 60 9 160 Kcal 15 05 25 소비동 영a밥 온입재제 프리 돼지고기.위 중말 유증송이  소비사 영업스  @ 이래 : 58 75 닐9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제품명 고구마형과자 내용량 162 @ 식품유형| 과자(유탕처리제품) (업소명 (주) 코스모스제과 / 경기다꿀 '소저제주사 진접습 플강픽 kI http:llwww csms co (스비기한|후면표기일까지 판 "to SII [민구#말늄지국 d-토코페 '엿 딱 새 98 % , (원재료명 1 청제소 크림해 알 남압 960번길 '캐나다) '창[팔록렉인유 (발렉8,1o ; l(혼합히] 탓 콩대문(한로_ Uo; 물 글리 '씨해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ocr_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>image_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>readable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|밀|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|돼지고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돼지고기|복숭아|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>unreadable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 돼지고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|우유|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두, 아황산류 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 대두, 계란, 우유 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두, 땅콩 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소고기, 토마토, 복숭아 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>#</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134642_jpg.rf.87d0fdc89cb54a0c5e18a92dfc97d4f4_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134343_jpg.rf.b355ae002b7cb468768f213dbacca279_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134401_jpg.rf.3d9bd20ccf494a7aa3ae8dcc32fb1f7d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134243_jpg.rf.70f5a394d6d4e8b7dbbc66c573e1ebfb_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134240_jpg.rf.a3472a2dbc06d03e25a793a45b56192b_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134633_jpg.rf.327ec502b3f860d4541a47a28709c5ad_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134646_jpg.rf.452fe6dc8181636d862e74e1b949ebc8_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134219_jpg.rf.aee14c8a9786adfb8bd36d9e6b8e3711_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134709_jpg.rf.97d83ad01aabec6bec873aaf8bada61e_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134717_jpg.rf.edbc6f1413bc42d5dfeeac027b17ee89_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133643_jpg.rf.6c69f3e3051a0711e1d9fcd9ae05ec32_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134258_jpg.rf.b5b5e0a48f4851716aefd7995d3e7d70_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133646_jpg.rf.d1d156215bc8d75c50e0fed0cff8aa62_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133722_jpg.rf.36af60d9cafeb74cd30a3850599b1e0f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133634_jpg.rf.753889fd0fce8764aa39121ac9f18adb_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134056_jpg.rf.7dbf04349226ca02326439c8cb63cfd8_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134912_jpg.rf.fa9ad12d1b6eec77586399144cf94d52_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133344_jpg.rf.e48cc88355eed51e52467cc0af78e13b_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134750_jpg.rf.e796a2b61a281428b46f40cd451e9482_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133627_jpg.rf.9229bc83ef7c2ce234bb6c908a7bb049_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133326_jpg.rf.4f05b90e1231f0a37a569ad728219b9b_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_135034_jpg.rf.fce49c5fd42aff4cf8d899b8ab9138c2_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133355_jpg.rf.932836217ffce9ecc65bb050612f908f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133650_jpg.rf.42e201bf877c5ec52e99d6d2f3c8e863_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133831_jpg.rf.3327be8e6ebb2ddcae58f556d7acce68_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133848_jpg.rf.604060740d2b62c4a27514dd5db2ea45_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134101_jpg.rf.31291d284c56619b567920454c551aef_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_133930_jpg.rf.936283b369c239e4469cfafd88abcacd_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133638_jpg.rf.96aeb186d920b46a12a704fece16edd0_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_134044_jpg.rf.3f10895ccad6ea809c916ccbf47d337d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133826_jpg.rf.1f05c7afad87c834729c4e69cf60ba12_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133836_jpg.rf.a82fbd4a8e62434e4006243ba19956e3_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133621_jpg.rf.c3887d6390bc4eff5679dbf75a4cc8d5_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133330_jpg.rf.de69efcddb15777fe221234b7399ec90_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133820_jpg.rf.f79bf52bfa23b06661c8bcd71e3817e9_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133656_jpg.rf.00a7cd51b1bc8474210a809df52eaac7_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test_20260614_133936_jpg.rf.e976887593a5dfdee0dfd24c75ea13b1_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_133327_jpg.rf.6ad8b7bc052fe267dc6cb186f362f394_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서e Oi 휴e '마 나트 탄주 왕 V6 Oiiil 망따권다 오a사&lt; 하: '배y 트 (실문요형 어물 신문욕 마시요m시리제포) '밀휘이시야산). '외국산(러시아, 변성선분 정제소금 형가리 '가플리유 가4 화이내조 킬미w하a다시즈님 산) 양파 흔갑세세(댁 양파 트린 감사분말 oAWo 라; 식인 %:" 제방 9e Vo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엎고주의 명칭 소씨 푸드움쓰올_"진영-포구- 양듣로 기주 1의대포침_제플리미블레_품유하로[가공표 스미가 훈련"기일지현필히 그번획테-3919090086DD3125리g신)igo3(4OO 원요료g 속잎 스챔로 물-교간 예라도로산) 컴퓨탓 잘숨 코코이다 {콤P탤스주되물울-유리적감용유품로하하다 올로때 [똑히-시진"진록요지훈 S기-피래 서r단 션 질골스오 없의1399 M비기t탕왜하프터 텍` M적전- 불하수-용 용요요중 주무 표회@- [치 영양정보 I9D Kcal L덕 LSmIHD EoaS 159154 'IIP) 포함지심2909 ISm??ng P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영임정보 Vagonoirt 꼬진 WJly YU- 225 ! ! 1 E 2! 6 914973"503139 보미하다5 고모끼: NBFoauy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카누 83 4 4 4 Io 437 l유 450 라떼 W oS자다{ 오aL 6C 에 너지 액티드 BCNA 에너지바 어시) mI DA 65 03 'mmo Q 백런스 CIEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|쇠고기|대두|우유|돼지고기|조개류(바지락, 굴)|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-EGG|B-MILK|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|O|B-SOY|B-MILK|O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-SOY|B-WHEAT|O|B-EGG|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>린0 말리 기타 댁린 힘유 @로움점일행 한천 '힘유제 조건제어모제베진로생승 %) (8959% l출 다요시설사트 일일길숲 플발콤플해탓 @혼고등 국번 M개류물전부 홍합 또 보심 가능 부덤 및 l사관신올 피하여 실문 텅각 '제조권 G5 산도조질제] P고"' '536 스고 {감미료) 식용유지가]품 산도조절제? 되지고기루송야 복숨이능-액 당알코올 171 D 말리돌 '알코올말터늄액 있습니다 '고등어계점; , "ui자kdy 모람) 잔 신고 교다 CtA 묻람식문 3311 반조 '고개지경센터 (070)4637 2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스_3 컴니미 짓스불비배표 미재유렇리지품 콤프룻-_ 소랫문(활할미국전 공가루 소먹문(밀 흙중심 도모 청제소금국산; 대듬문 유회제; 팔위말리이이엔) 증문감자 l입제제 (화따오같등잔률 말토렉스트린) '기플리유 말 정제소 직고주출농국액 햇지즈명 남차 밑 쇠고기 [토미로 유유 조개료길 힘유 소미기라 주면 표기밀까지 포장재질끌리프로필렌내포지) 19700342001-256(만입) "계로 새우 돼지고기 (전목 '땅콩 #수늘 시용한 폐 좌 올용어스해터 제조하고 있습니다 직사관선 '피고 서O하고 긴스럽 구에 보관 하신시오 개념 무 바로 느신시오 과사메 미는 주무색 "월자주 민류인 파v리 이오니 인심아고 느서도 소비자기 번에 희기 교기 드리나다 비없이 1379 영양정보 C r M w 버지 가듣 _다 W; 데다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>" O 9 DRIS 서AIT Sable 사브레 oKIGINATEI FR&gt;M YKANCW "I &amp; uA'5Cal UEII 1076 버디 해) 사브레 ' ' '; SS '849 1,600 ' ' MUIIMVW ' I O TCDT 리자 무N 예Y A 도장재심 "리다 _리내터 리 내행 %0 BaAD'OUS22I 영업소의 명칭 및 소재지 기0가;: 메미국신) 삼답 소다 {납유주#되레이시야신) (미래미시야 렌시터 집시' 뉴님 마; 리아세다 @입하다] 리서긴지밥산예스데 대누무 리아세다루 '비 I민I? 성합다 "개대 그시어 3내하다 * 들기' U어 '반합' 교실심 [전 떠고가3불l적 DIII 사과 국어없이 1399 eloen 데주시 버시 깜ut고 VwFtuk 93 9 399 ! 급굳이 스애 3그다지르 '일어신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두, 쇠고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 달걀, 우유, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 계란, 우유, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|대두|밀|쇠고기|달걀|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|오징어|대두|우유|새우|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 쇠고기, 우유, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1E 버터와뜰 '버터와뜰 내 용 량 135 9 소비기만 세품 명 플리프로결렌 식품 유힘 과자 포장재질 프프러올-과 다다 품목 200802423765 월소망지 주덕주 07 보고번호 및 보지명 물기로_말-미국스닭 그율버뒷번물관- 완하다_ 줄자m그름렉_ 소현실 저 해국산 홍중 흙 정제소금 생국럽레신; 조메리 함료 밑 대두 계란 우유 함유 'O콩 다-그기 쇠고기 흑입 영양정보 가능 교환 켓 반품 본사 고객 상점실 및 영업소 혹문 구입한 100 9담 곳 직사랑신올 피하고 온도' 습도가 낮으염 둥둥이 잘 되는 나트움 340 img 곳에 보관해 주십시오; 단수화물 74 9 부정 ' 물탕식움 신고는 국번 담류 y 9 '없01399 소비자 기본번에 지밥 16 9 의란 '피해보상 09 '(서울) 977-2580 (주신치요금부7)080-709-2580 또화지밥 I' 9 레스데 95 IIW 단백질 맘 학 Pa muller 신일서로 트랜스시방 | '고객상담실: ( Uel V사 시대 어반히벼 O터리 "7oiil 73709</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어; 아이비 ('쿠 d 25 % *% 50 및 식a 텅 6I 유유 C 구 조원 단 I 돈 및 9 럭 C 9 여 8 pOCKy 스틱 [대용광M '바싹반 초코스틱 ,미국산 신시 [조'릿가공품 '4뇨 #콜리과 _ 버터신도? 코코아매스데표관드산) 가공유재싱가포르산 , (리 . [밀가루만호주산 탤써스가 [포기극세식품유형 1,항료5송, '피컨. 프로 유화제]; JigyMAYYNI '정제수 , {합량| '코코아버터 정제소금; [제품영 흔합제제치자방색소 [원재료명 소제 꿈목보고번회 요모 이어신류 입원 '전제2 소트님 [제 유화제2 사드조 '천인2공장 전391 (대모상면 이까지 구색소) 기념'다 '성거다 해탤제과식3(주) / '씹이 a로 7? 가다 '한강대로 스비기 '고 '꺼0시 포장재 집성거; VY) 국리코하대주) '피하여 Gaug 겨쩐은 N8 보명시 2543 {유용전원) 스신 숨기신 구멍선이 주심시오 고인순 생 신고다 y성 오르하여 '굉장식협 그적오상 모다 구입원 우 [회거 ) 모새 F:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설탕|포도당시럽|팜유|구연산|덱스트린|변성전분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|O|B-MILK|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 대두, 토마토, 쇠고기, 닭고기, 새우 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 땅콩, 계란, 밀, 쇠고기, 대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|O|B-SOY|B-MILK|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89 우 제 P다 8 700 엉양정보 싸신' 80"9 내#yi 489 단수화다 09 09 당류 209 렌스지빵 99 Oa 지망 포라지생 스U3 '8020 대부무)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥순수 뵙이 '202600231m 제품명 옥수주트이론 제품:! 특 의문유회 [스주껍"_발[ 교질 의 겁질다 눈음 업소명 및 실현대로 @이버길 30 속부문만율 진로주 소자지 컴프기인까진 입맛의 감혹바 소비기한 교oag@ 때 한걸 더 헌 불불델면렉 국산 호주 부 쾌가 가표 (리국룻되-꿈록g이%3 자손만대 옷 제탑10% '문a유외숙- 태 현료명 중리4% 국산 만레이 국4드 '생리렉트 양정보 대무 입유 호갑답 킬로 J75.6m요 힘습니다 71 밑 뒷티이 = 도에 '히집o 10.02 제 어논 Q 소비자 스시 we 이 미사 건조 오 혹수수가루(외 {%,깜유외 시O)1.59 , #리프로"로PP) [200406073143 49 가동설인 . 큰입 회으다 따력 저U서 마지)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥스다 K 09 이 mI [H 소 O 이 (O 6 거개 기) 25까지 2026, N리INa WN '제Iila GM 입소입 기인N 소새N Ved OOaliBokCa '(0EN 'io 109 없새요버 06 'Noll</x:t>
+  </x:si>
+  <x:si>
+    <x:t>로M길35 7-7 오다 싱가포르산 I35 탑 기D W망정보 400 Kca 1274 1ng0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5 cp 신 '셋 생 * 수 이o 셈 ? 9 '%% 시o @ 4 시 739 y 2 J 5 7 혀 '양 { 터 명 ( 록 북 1 법 6 평 C9 털 약 1 품 { 뻔 말 [ 몇 @일 1 (o ' % 7 @ % 롬 훨제3든 턱 8 #</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스진I 형웅싶 소재지 햇방적관실럽엉중출로록 리로 훌어운출로동 임신시 울__ 플함스못 킬가루 밀이 소트 [말레이지이산 휴치예스템름하유 임어 면래움이야 발하다이 하산) _ 동록성유자 위땀 곡루가 앞심렉학심함적 테오레친로출메량 성류 움기탕-유성콩적지물히적젠f훌 전용없라유운- }워"다 출성용물 비닐물p용 o T 학유 밑 쇠고기 고기록 8신 {깜구 기공유크관 영양강화제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3w28 3심 8 2 S 9, 78 9 임이 06 Y 의+9 &gt; NS' '6s 83 8 8 1 6 5 ' # e (A ; 무_ 근 I 해 " ' 1 ' 틈 5E30 3 틈 '뜻어[하나 틈 " 점 코코이튼 분 @ Jun8 {물정유재 N 면 (트려어사 방 J로 콩 3634 '4i, 8 '#;력 Nm ariasan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-EGG|B-MILK|B-SOY|O|O|O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-PEANUT|B-EGG|B-WHEAT|O|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 달걀, 우유, 대두, 토마토, 쇠고기, 오징어, 조개류(굴) 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 쇠고기, 대두, 우유, 돼지고기, 조개류(바지락, 굴) 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VI 4 탓 #붙바니# 볶대렉빵돌백 [음워운 (소먹분말미국 [미국4 호주산 로모 공히권 방젠편 [유회재_판휘끌a이 이원 중망 _s다 (타피오가산화전분 말도무스트린 옥수수전분 지런주출놈주댁 엇마빵 [분말 정조금 따문말 '둘기트 토유[미 r콤롬" 포장재- 증급 @콩 중어주유 g웅 5 '전물 올물도함다 -이고 개념 5@ 깨어다 이오 물 -고기 [렉로 43미3I" 도 무보고 뚜" 고V '앞애이다 '자 세조고 '직사공선' '하신시오 과사보 원지퍽 뜨다 소0자기 정보 영l른</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-MILK|B-SOY|O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@기렉주면 포기일까지 (품목보고워5 용`질원트 칭 [탤탤지적룻출- 하로륭통흙 아산발리로 히또위%@ 재질 프로필렉내면) 무면 {미국산} '종륭회광원임레어실이고 [정어심하다" 운륭 콤울플렉빛다 흉말렉요시야신) 광유(리 맵립임성 패탤용소록월플하렉인원록-의알 로로 [통플등등적훌출 기플없다지출쎄컴 탕 활중-각운-푹록 일학훨제 서성황록- 비타외l록슬음-t타eBs 합제제료 쇠고기 {알유 가루밀 .양</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대두 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|달걀|우유|대두|토마토|쇠고기|오징어|조개류(굴)|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전 조골렉과 바싹한 스틱 pOCNY 벌려스가 중은 초코스틱 [제물명 [포키 극세식품유형 본홀릿기콤품 내용량4 9 [원재료명 및 합량 |밀가루{밀호주산 50 % 미국산 25 %)} 설 [당 코코아매스(데덜란드산) 가공유지싱가포르산) 전지분유 소트님 코코아버터 정제소금 유화제t 향료5종 버터 산도조절 (제t 유화제2 흔합제제치자황색소 정제수 프로필런글리출 홍 [국색스) 산도조절제2 효모 흉소제 우유 대두 아황산류 함유 (소비기한 | 밑면 표기일까지 [품목보고번호[19940449005191 [포장재질| 플리프로필렉내포장면) [제 조원 |해태제과식품(입 / 첫안?공장 중남 천안시 서불구 성거움 진호8길 67-26 [유통전문 |글리코해태(주) / [판 매 원 서울특별시 용산고 한강대로 7긴 3(남영동) "직사광선 및 습기찬 곳흡 피하여 서늘하고 동둥이 살되든 국에 보관하여 주십시오 본 세품은 광성기래위원회 고시에 의거 피해보상 고개만속실: 수신사 요몸부다 (080-333 16677) 부정 십림식섭 신고논 국민없이 ! ANI 반문 및 n다 청소: 본시 및 주Pa *이 세,은 '바노터 사농i 세a 마 간은 세소시신에시 새소히 4 깊심니다 *;둠중 온도 네 (뇌에 미 하인 반신 나논 하진 4{io이 새리 수 있우나 인 제에 무해하다 '서 "카니다 2 ( 이하 보관하시면 맛외 Ix kY 예기신 싶e니다 대안w : 내에 시 민 판매 ) 허용민 세습씹니다 WWIM CuAI OLuZtCal TO WW 8 7민주요 F8나 아제리; 150 5 *</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1405 ' 조관접 74 Tnr OoN rkso 'oNuE 스타일 쓰라우니 (W 카때 V Mared D스: 17 화선님 ~건문' CBBn9 초 (5 %트 Keto ^및 고심 대한 78 2다 '리엌 럼 톤 )re 초코 년 2좀 대뉴 환문 429 8다 3 쇠 89 83 밑 당류 419 , 미만 P5 최시 개; 지방 059 {4다 rg @ 새우 . 219 7 ;두 55 심 곳 {6m3 2e 딴 및 낯은 {9 채 반물자 온 불망 다 인 e 의한 국단하이 개봄 보관 0- 0y 둘 무성 고객' 로자 터 MYw '"a 신배시고 로u 건기심 레브닐스 = 씌다성유제민터이시야신) 호수산베터지다 오리? 대P 그조이 '가공버티 940 '재지] 잔셋정매당 , '미산) 민가주 (민 유어 기타선량 배션 (영양정보 N3# 국고하버터] 주0 영망생군 '재 "합제제단산수 소나트 간새신딩 유구램, 신린액 똑아로산) ' '기준치다 어개 텅 Fye '살가루 기당언규 쇼9 (나트움 '인산다다 민1 창료 29 [단수화다 우유 식망 신성미로드 부수버터오이 05 9 미솔 달간 '돼지고기; 조개류국 토마도 신단경 복숨아 트랜스지방 하면 ` 리 오징어, '집소중전 69 포화지방 '당고기 기준지석대반 비S온UTA 손입기능 위해 구입한 P수W나다) 보존움 곳에 (플러스비: '대수 모함) 본사 신선도 (@캠^미피라드 습도가' 단렉진 드세요 꿈의 {영양성분 - ~가인의 '피해 불리 '피해보상 1339 '가급적` 기준미모로 '식사장선: 570 '기본번에 = 신고 '량식품 비자 (전화) II 센터 152 ?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S 유통전문미 ) 못데웬포드취 서물시 영등포구 양평로21길25 제조원 국제제과쥐 중청묵도 청추시 청원구 오청흡 과학신업3로i88 제비기한 [연요기일까지연월일) 직품유형 [과자 품목물고번호 120010415034793 [포장재집플리프로필렌 원재로명 (식물성크램[가공유지싱가포르산) 설탕 흔함분위외국산) 8 80 (혼입분위 유당 말치흔합분말] 밀가루(말; 미국산) 소트님가공유지 관에스 l테로화유되유 말레이시야산)) 판유(말레이시야산) 우지 가공유재 팔스테 [야린유] 기타설탕(원당 전분) 코코야분말 전관액 흔함분유유청단백분말가 (공버터 당류기공품 변성전분 정제소금 산도조절제2종 커피농축액 글리세린 [지방신에스테로 손합제제합성항료 천연함료 주점 프로필런글리i 젖산 글 (리세린지방신에스데로 정제수) 바닐린 무유대- 고기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I 9I II7 M개시 UUUIU' '</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 우유, 대두, 토마토, 쇠고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[현관인) Ty9 어언 d애U니 바마 -기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134457_jpg.rf.e6b8508e9e5ce7a90ea9d49c2efc7473_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134252_jpg.rf.1a10ecca006dc5c4c20bd5c29f217bd9_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134428_jpg.rf.2049c5d825fcaa6fc9e1b2faff46e48d_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134152_jpg.rf.34350a82e718c40cde60fd81b9f12141_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134011_jpg.rf.08bdb8c3164bc63c496449d14dbe9864_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134218_jpg.rf.a4d1c3d0478a16e00791234c97797429_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134144_jpg.rf.3d2eac697070e6189daeeaeb7208d789_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134332_jpg.rf.57398403f0532065a14f118a7bae2e33_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134018_jpg.rf.abfe047d302ad80dfcec54e925050521_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134452_jpg.rf.07dee26761afdb0e017c1b4270c29e60_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134119_jpg.rf.eade0face448cf26d1fa1ad54343f344_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134424_jpg.rf.5a5c3c7ee9ab5850c8302f6fcb84ca18_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valid_20260614_134336_jpg.rf.ab4506c3110a6df4bac04f4465f4839e_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134434_jpg.rf.3ea558dceef5998006bba37b9839410f_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134419_jpg.rf.c7b189faeee04139c48c432ce16ebdc0_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134440_jpg.rf.bd9b05ec7ce0d5619a3444b493ba2df1_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_20260614_134250_jpg.rf.cf2481ea6f846741c7157ca4dc4d12c4_0.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|대두|돼지고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 쇠고기, 우유 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 대두, 돼지고기 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-SOY|O|O|O|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|B-SOY|B-MILK|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유, 대두, 밀, 쇠고기, 달걀 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우유|땅콩|계란|밀|쇠고기|대두|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|대두|토마토|쇠고기|닭고기|새우|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀, 오징어, 대두, 우유, 새우 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흉내내 PIO G너| 나 비스금 일 유당 설탕 [공버터 당류가공품 전분) '전관색 [방세럽불d하밥-방@ 감신도생@다 무 [리세린지방_에스로 햄수 바무 주정프로런_다 신3 ' ' 35n8 LC 제조원 어물시엉동꾸구트 제지미취 과회산업3로 '양로 중청묵도 소비기한 청수사정원구 '188 [면꾸기일까지언 요음 품목보고번호 120010415034793 원재로명 [식물성크램- (혼합분위 기공유지상기하로미) '말치혼합분말] 등 (테르회유금유; '밀가루말E 믿입분웨외국) '미국신) '말레이시야산)) 소트비가공유제업시 [야린유] 기타설탕(원당 _ '판위말리이시이신) 우지가공우새장스 '코코이분말 _ (본일분유-유하다 눈일가 변성전분; 정제소금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쇼 집 팀 액 '힘) '밑 석 7 '수면 대륙 요요물우 원 머무보' 마도 산 게 와 I사분 관단 재표명 [오징어집 {버구이맛 (맥분(말_ [옥수수: '미국산) 식문요영 (인재료명 '외국산리시야 [오징어유오징어 외국산 깜유말레이시야산) [재요당_리 [인산니트트 형가리 (오징어맛조미분말 세르비아등 '버터구이오징어맛시증 옥수스 소비물드 [자주색고 (이맛 플리인신나트 '구마색소 소비기인 오징어맛조미분말- 오징어 [파보 카카오색소 오징어주리스 고멘호 #기일까지 @대시고기 텍스트린 [19910461101 ` 입유 g리l o이 되고기 'j성하 (생선y 4리) Io720I54001 E 물리n로 '미이자 '사궁히 신? '쇠고기 새금과 시멘이i 신수득 1"세세 #대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허미 공류 극타 @ 히대물물" "De1o {e-르an 6 3p85385 lo81 훌g@늄 le_@ lon표 너n 매로구 R훈 @롭요( n돌로다 모mlai TX: O9Eoonon06g6l 또S으이 교U뜨누_ 더테이터위; 기WI요#MlBTa-CaUE_a LULili [UO데하 트 표Ouu 임류; 근냉 BOD6LESIObGI LuS 7 [YEl고공움다_(지리 +가끄 _이르트-0프기-하`C eJ9 S81 6 7C 유해 ` 7요8g IC _|프프 [머o지순 (3 3리3n 글3R_미미야로로 {lD} O (머어프준 공관_ 고로준이프골 B료 (CrAY' v?D-Urma 모_프 &gt; uWha 도TZ{유지Z3위3 OJT DDIT ITOTTTIdTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크 버터오 2,600 [내티q뜰 내용량 1g 소비기한 믿면 표기일깨지 몇 { 지 (대전광역시 s팀 6번길 57 'GA AePP 국산 밥유 = 푹 곁 II '@텅 Ii0og 4y '비표 타수 'M '허리 '대 / It} 17 법유 7 0 % 시밥 썩 P 1 Y 3 F '시법 엔 '세 1 9 80 % 9 92 % 19 % U mllle 수발움 물리프로필렌 WWA다: 업소명 (크라운제과 / [ 머녀구 = 신실서로 소진구신 '가공버테내덜관드산: 샌소히 {드립구진 '유지방 (전관세 "신드조청제2중 , 유화제2 출함분유; {'과재가공품 , 올레오레지로 엉양정보 (N64 '45/ 'kCal '나뭇다 8장하신 I순 또화시미 W' 'WX Ko 와U'1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[려; 해매버 미 @i하| 7 인 '#로 [제기해 호; [쓸픽워 떼비 l월드 탕 [ a %공유34 #너 I야 7J x [지 p대 |쨌질드 (국산; 다두 (무 입구 #시히 ma이 UII M 믿히다` 인대잡 O6e 1 MJ" j0 ^ ; (오오k | '무렵 소등 (소지 '#Qa오' '4외'} 디의기 {후어표]버T지 '식물성유지금올렉민우 '뒤경씌 스고스 "외국쇄- 퀴 {토도뉴도도_ '마음노신:; 중국산; '최국산인도산 '497터- '사괴능주자중다 '드t2보]대k 발요식최[ 1귀신; 겨고기 = '인도니시미사 ' [브매치간핏 ' 7937 onioN {#음넷 국씬 '쇠고}_ {도미보 I0 F4: 47 오119091 300 Naa너 실 미다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C 드 43 소 - 낱g 구 로로) Tgmmtran 유수 문 상' 식n유영 마작 중말 D8 0A위 암기유 '3유 오징어 P: 원재로명 '리서관; 포도텅 주머리 여 유장 50599 '터시린 (텅로 주인 25 0 패x - 보 시드하다 beeri 0X23제 정요지 가공요요스요389 분히스 06433오3신로조 99 호주진 어스러로회위금스터야린유하ID 인기루만 미 야사요 은현보다 '8제서 {하오현v리 식_성유제럽워다하이시나신 스웨이린요라리이시야진) USa드 MI 흐려오러진서이제 코모고어금미만3이)이신 '합리시청러인신어스t. 성물소 88? 올리오리진서이째 렉사 수수진 [g로고르3 비 '가려시' 외FU 표기인까제미입인 ': 신문 L무소묘보g다 강인도 소비기한 | 유인회사/ 인신표_O 미기망 바 [용시시'주 제즈원 유용신문만대권 O83 '9uo u 딸바</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위시로로 입" 제2 우지 및 밥표 3y' 큰o 게; 대내 재우 4y 대두 빨리뷰 부 개본 설 위해 뱀 군 EI 늙론 GrOaTN 소비기한 마지(운처리제a 도장재집| 식품유형 볶음양교맛 전북특드자치도 [고래밥 19760487005105 인도9 제문명 의신공장 알따옥수수문말 (옥수수 '부움양넘다시스 품목보고번호 R오리온 호주산 ;화다 변성전분 '바메규양님-이스무` 소재지 말레이시야산 미국산) , 업소명 [밀가루(밀 판율레인유 전문 식물성유지 원재료명 말레이시야산, 함유)) , 괜료(a) 아스파람(메널알라년 불화조미식품 소개주3다 (판유 호집어` Jdn 쇠고기 기본범쎄 산도조점제 토마토 'm고기 소비사 새요 '돼지고기; 갈습 사용하엿 습니다 _ 우유 '가타색 목숨이 털걀 호두 '방식롬 땅정 보권 공기주입 구입다 '국예 낮문 습노가 본사 반표처 399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>63 으 년는그 박-도 92 기뻐교로심통 통극록록런로레이리설탕 훌함문유 (싱가로르산 전치문유 코로야 리어이}공h집발_이@/ 승렉@훌뭄_플하늘록-올들이지하양 스템가린다 훌t궁콤스되다물로-출라이스이하 설통갈후플플렉@름 ##lR성가도록 전지분유 '말레이시야산)) l분별득 (말레이서 가구울산소 너I{ 글$ ]절라린 {유당 코코이분말] 설탕 '훈함제제0 003 %(주정-5 26 빌로 ## 빗트 훌륭 중 면질혼온 울유 대투 돼임증 활유 중요 가본 실골늘 국7없0 53y3 구입살점 본사에서 교환 조리사; 중포결 모면이 인 제문은 로소중전 포장설 적몸 [정금포장교 하무 사용하엎 습니다 CaT 코코아매스) 가뭄유지(경 이라데야검 카나우 눈함쪽 'I5 c Ow자 정무예서 라인찬 주소하다 드여도 H 색기급 ~회진j 반V &amp; '03625 없이m 430 Foal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dLU U" 파,다 ) 재요탕사 때 '제부역 내다 목수수진부 '기 기늘기위 형가리 '트럭미리 {외국산 소텔액 (원재료명 |안a니무차 직 발-원 적무썩쇠 '텍스트린 실요어대표요요스오백 포장질 소비기한 |후면 @문문요 j@om@@] 계란 땅콩 @돼지고 도미토 퇴과짓 게 '같은 @전보 공합 #함물 시용안 제품가 = S습니다 "시장_올 피하고 서늘하고 건소한 곳어 바로 느(시오 "간로 제금예 신문 간색에 | 검은새 '방화 U는원문인 요장어 흥미 일부분이로 ' 느썹오 소소기보내 의사 교원 비맛미 특징" '부성 불림식품 신가{ '비늄 년기넷 구입선 신뇨 ;시 신 형양정보 F7이a Px집) 깜씀밀내 "미과 맥분(빌 미국신) 세르비이 '외국센리시야 '플리인 ' (옥수수: 오6어퍼이스 (오징어유오징어 ! ,버티구이오징어맛시스님 오징어맛조데년 (오징어맛조미분말 카키오색소 [지주색고구미색소 [리"로보 고기일끼지 197 19/20154001 쇠고기 '시실어서거다 서구이맛 '보랜하su ''배" O77 '인닐에 '1399 최어언에 oay시l '6신:심다 어대 WBV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안산공장 경기도 안산시 놔u그g 일까진연 코코야 G바라기찌미국산 류출록지중렉-하평탕 도)물유 롯갈안활장가포름플팔-[동압 패스 '가공문3-이하0 }공유-름팔소_기[림예승렉록록출(위왼 설들각루 중화 함분잔유 (말레이시야산) '울달 망코이분말] '말레이시야산) 글랍출무 달라이 원재로? " 콩휴지 팔스리하리예스레블화유(팔스템아리유 숙요어붙말_설탕 기1 마산) ) 싱가포루산 전직문유 코코이매스 유탕 허(주증75 칠다) 화구) '로유 물엇 아라비야검 절라t 흔합제제0 우유_대드 활요 {자) 비타민터 본자에서 터에의: ~늘스패 들다 초대 진월 유통 중 번품안 구입c픽 부정 불들식품 신고는 국번없이 1399 이 제품온 s둑 탤콤포장재출 및 하소 n루 손입 가능 .유능! J 춧골권 표면인 새기 ; 앞하다 먼제에 무해하니 드시도 사륭하없다 위대 진소3전 포감음 하룻 다M = 시원런고 E질보손글 입적 뿌리 심시모 (놀럽 80 9 430 KCa 4713 11 `7 야[ 또 회기램 10 86' Z0 . 어돌이 @스 유지경 카나우 003 보교기 사' '과인관 'y부내 사보상 진으</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뇌) 얘기 ^ m 2049 및 논 소비기화 제품 명 원회 설탕 소쇼톱 '유화제 피정 울 홀명 없아 '우지_ '프로 401 화 도당 기공버터 호소제 진주시 원 판대 권 대 용량 축머표기일까지 샌드에이스 우유크림 대면) 흘리프로필렉 스레 '소트님기기공유재하스테아린에스 과재유처리제물) 포장재집 식품유형 19820481021366 (레시린 d-토코폐물(흔합히] _ 유멩미국산) 부담 '기공유지 올레오레진로즈데리) 기타성탕(설탕 전 품목보고번호 밀기루멘미국산)} 기타기공품' 기타가공롭2 르회워관스테아린위만레이시야신))} 전일영 곡류기공품] 곡류기공품2 소트님3 마기린 '기공유크램유크램호주산)} '깜스테아린유 '텍스트린) 항료3 유s| 제품 (넣리핑올레인유 '연세우위원유국내산)) 핑유 '테아제 분) 손합식용유 k리제제요모주출문 '정제소금 건이다넘8 (@쇠고기 무유 대투 함유 판과정로 (항료] 항료2 어진모 ,이 산도조전제] [제미리심터 (조전적무미지 제신도조절세? ; h닐엉터) [해대세과식국쥐 723L 제조 {인길대로 유용전문 시나 신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'발춘가공하터 36 &amp; 과자 ( OKa (도 WJull GaLIa l해 = In 비터동미 해 버터롬 골등 'uullo 2업 내H로대 해대 버터림곧드 6V 1.550 ' 8" 고심 ~22VCOSTI 소비기간 라국씨 식문유: [래오래진 스나근 깨규감 R'I {레인R'문하지이 음_다하로3_히이)야샌? 대스쉽 입성히코 아리비야럽. 지로델 밀기주 (비미국색) ; 소문울n도 던;) 유리제 'T제소터 입금저재 관5 붐내다 ' 미가신 '기공치' 기니기 {포집재지 교의 피뻐션집 입규 종터? 하' 27 고자m 미 매칭 햇 소재지대대제 잔 되는 고어 보과히여 진시모 및 교중님 키 구민신 및 습기신 미하이 표f이 t드 [함사E 신고히 국없미 사업 ; '합갑다 "무이 NWAACC시 개반 ? 심; 수신자 요a 뒷예 7과 # 제소시선 선 제스하적 만부니다 이 세금로 냉젊 신고기 사목민 보"과 O @;하다 어러 @ # dDDM AATA goy8기 N 1 예란과자 8 Gos 명화제 '그래: 누_비 GI7) r 애덧 b섯 806 5o;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0 (%)) K 먹먹는 분연의 동크 그미로 우유 ( 스 제 풀 명동크 초코 식품유형 | 과지(유처리제품) 소비기한 | 믿면포기일까지 포장재질 | 플리프로필렌 업소명및 | 취오리혼 제3의산공장 전묵특별차치도 소재지 의산시 통서로 377 원재로명 _통크 조골릿(백설탕 식물성유지다 말레이시야산 전지분유 뉴질랜드산 식물성유지2 코코아매스), 밀가루(말 미국산, 캐나다산) , 전립분(밀 미국산) , 식물성유지, 백설탕; 알파밀가루, 식염, 산도조절제 우유 대문 합유 품목보고번호] 19830487051139 달간, 땅콩, 호투_복숨이 토마토; 돼지고기 신고기 타고기 오징어 대후' 게 '소개류(물 콩합 모함) 종입가늘 소비자 기 본-에 의한 피해로상 "취진공선흘 미해 콩 숨문가 낮은 떼예 도분 개T루 가급적 빨리 드새요 고객센터 (전화) 080-03 5700 (문자) 1522-4002 부성 '불랍 식물신고 : 국면없이 399 반갑처 본사 및 구입한 곳 내용고 458 23619al 영양정보 3 %0 [민수화물 28 해당; 16 3 16 나뭇 '' I터 사화시밥 1 8 47 지빛 12 팀 22 % 스시방 0 터 7 컴레스 %라배 4 고 끼운미내 WI NCCI T20su0 방법 {이미스크림 8 9 '미민</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-WHEAT|O|B-MILK|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|O|B-SOY|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B-MILK|B-SOY|O|O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|우유|대두|토마토|쇠고기|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>088 28 403 다리04/ 어가, 미니사이주/ 파디 '나툼포3되어 보관 쿠대가 감리/ 리온 T '7 고장재집 "리프로미; 미국신 외 기물보다 식물-무---슬가 불g 회지출텔 . -컴무지심유 (샌후장유생동되이시야심) 전지 _신염 '땀플레인유 우유 대두 소바다 ?액적 손리 의한 0' '부정 개 ; 중 4002 신고 피해 a 습로 10 ; '80 8140 반물치: 및 1399 오 17 / 곳 1 8 특-치방 8 % 8당 10 % FB 63 40 '떠리다 9 8 제 살 3 " 어내 No4 가` Pnet 5 알레이시야산; '편지늄유; 오드구런지 신도조핑데 6 DI_사과 물목보고런오 719760487005157 함유 도마도 , '돼지고기 &amp;^ 직고가 기본범에 닮고기 오징어 '피해보상` 재우 050 드N요 직사장선올 영양성보 '조개류 ST0 풍 (문자)1522- 중앙식꿀 ' 내용량 굳 '국번없이 m 본사 '8X 2봉지) 국주스옛{ [보소화물 구입한 @5 1봉지(40 308미관 20B VGAFV 실 ']3WT버터fW? 197 당류 '단백짐 O8 kcal IO8 포화지방 (주오리온 38 58 O디e 라니의 S HCO '입하다다 801117" '280512</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예이스 유리 2150 해)에이스 _ 5S00 ; JU4 980 V JI 캐 이) od PDe) (엉남정보 O : 09 [죄당 지O텅 진드에미스 무요로 소비기다 문요표기인짐 )다 '지O 기 쥐 _유어 고재롭증터제 포장지진 도금품동재품렉-하린어스트 요;로사하 허복금기언- 미해보 실물표호 '9920u8i03 % [발퓨 @하- 후흰미뜻--_물히다요요 재료- @a@놓 고기만 수선장_ 권기 명 '유회제 레시린 d 기타_템입전||듯러0h 주9 지 밝히 불l늄하p이j -기물 -자련_탕다름a다 붐O-#피로 신고트 [물_- 제인움 O-가하큼 유국유자강궁-시가_미기리 기표내u 한입업 :이_a85 모현지 [불 지동움 정제}자현서문위공워국미-_갈주이[체유국즈lay 요{유하 -로" [토론가공내다 8저속로현세오--기 -콤품유 이제 스끗 지불교공 T7 [신도조건재 . 호소제 말 구해R도 진회.진구 꽂과정로 2외되로: 자언 '무르게 년; 꽤 i0다오 제 스동- _ u l_조요자지도 1모0 MhCoWI 따리 제조 원 W 주무 대 꽂-치훨전모 희카대로 그즈럽연터 판교피서다 시 #뜻 ele 3 &gt; 5 샌드 P비야 W비O 시하고다 피하어 '관히다 ek 회로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'이미s {Ni워 애5M 95장a*기 0' 국결내} { {* Y청w]l8' 79 2봄입 1": 383": 0N3 939 1,400 CROMN ' OAN 9 거 WSII 은 그번 #기뻐스 임망 내 음 김 99 고소기 밀콤샌드 포장내신 {엘리"로 민레 5 [업소명 맛 소o지 (취하세기 Cri이시OC사]고은 심금; 하현이 시야상 -불# 단수} W? ~NnAZTGI% 인-만없이지야템_ 별_ 입뇨주 -"#이시야진@ 중E 권 불히다 업월물 텅 ml '밀기 퀴미 미국산) m트템뤄다 '점금문문 사 n습 품국산} 덜시 로대산j유회제협 #다: 비타민도 대잡리 '지밥 정화대#적다 만_이시야켓@다다] 햇당버다 설뒷 밝화 '청제소금루 _물장문백 국내산) E' 신도조신제3#; 메중국신) 밥유 '및 굉섭스 ;온 구입히 고 #드되품유-유-- 임기; 고 입 고 방째 '주십시다 개권 피하고 관도 ;수가 '어다 많이 미신 씨내심 '식사관선3 국민언이 137 예사 기쁨 무심 시다신기 "심사요급부탕M0-10}-%M "과대심터다; (Aaln eM0수 yWa 땅콩새드 고소한 ( {입82712X {aljyllzl ' c하스 이스 c어스 회번 신외서로 ,전정버 12 '빵하버터 , 고개심다씨 K ''에</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부: 통크 우유 제 품 명통크 초코 식문유형 | 과재유처리제품) 소비기한 | 믿면표기일까지 [포장재질 | 꾸리프로필럽 업소명 뜻 | 주요리올제-의사루장 전묵특별자치도 '소재지 [일핏콤록실렉철등 식물성유지] 말려미지i 52 l름롭플플핸플출__-요 집물영로자 쫓하 하 전지문유 뉴질런도_ 미국산) , 백설탕 RII '미숙자가나다-;_ 밀 우유 대투 참유 호두 동: 교해해출? 날은 달걀; 새우_게; (전화 83 오 예입할 피적 '부정 : 불람 @론0 개통후 곳 20 '본사 및 16 &gt; 1y 74 3 % 0a 55 mE 22 % % 시방 1285 8lo '본언 그따런 이미스크림?' 식물성유지 전립분(말 산도조절제 알파밀가루; 19830487051139 되고기 '최고기 돼지고기 , 품목보고번호[ 소비사 토마토 워입가능 복숨이 "슬도가 땅콩; '조개류(굴 '0* 027 '피해 '직사광선올 국건#이 '고객센터 . 징어, 피해보상 '식훨신고 빨리 드세요 1522-4002 . 가a 구입한 (문자) 48 5700 내용림_ 반물처 [팅# 16 # 399 '흐 9 '모라지) {민주의 영양정보 트랜스시방 스스 {단백심 나른움 UA미만 V84 0무 플레스데로 'I6 UN 예미히 Veo300 il</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근 6OO 크라운 4 7003 2 60T [버터와돌 꼭자 내용량 135 5 고대' U로 신립 신입; 대전 계만 산도터 Iu '무유 활유 23 , 년사 입 2 I00 9탑 "대 탑 시% WN billtr 내 (n다 ''머티라&amp; ': ?A ` #두새: 밑연모Ty리 시멩기 'NFXYUA,5 소비기안 둘리프로필렌 '7PS' 엎소대 5 '히;;; 'x제지 자그라운제과 / 요거R '미국산) '대디구 '거 스머리 'L어입남심 '경제 가장버터 서로 밀다도 67번 '전화국산) (네덜관드산: 조리재 ' '모기고기 과재가공꿈 '식고기 '합분 드 고 영양정보 구입다 '미a '나뭇 O '민수하다 {에 rnu )yII 퇴w 6] 시 '화기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가득 리론 곰 면 "프의 더볶이 170 내 중망 기새유탕처리제품 식문유험 (탤로명 말가루 { 밀미국스 )} 설탕 출양 #인유(말레이시야산) 고울 [떠전움나켓_"유-오주3문국 @- [메출혼합형)] 분복합조미식품픽묵 이맛시즈냉{떡 (국내스 '기타설탕; 고추장 파 [양파분 마늘분말}] 쌀가루. 어어 프리카수 충색소 (천연장신료(피스림록 '@유 꿀2환다 신꺼 잠빛 리에터 연어소의 명칭 소재지 품목보고번로 리입니다. 식용수 '베이스청제소금 '(중국산) . 심세소금 산도조 신도 레이 의대도 도미도 규기인까지 소비기화 ! 엔내뇨 모장재진 '해내제가식국 수) y구시 '심중보 #회 브대3 침수김 IS MMI' A MI신:</x:t>
+  </x:si>
+  <x:si>
+    <x:t>너시 먹들 로리시닐) (식품유-곡류가공품 [내용량 | 70 9 [현재료명옥수수 659 (미국산) 소트 [마가공유지(팔올레인예스테름화유(말래 (이시야산) 깜스데하라예스데로화유 애 자메스레측화유} 대륙유외국산 아르회 티나 미국 브라질 등) 가공유제광경 (회유; 항료} 기렇조V미국분정생소움 비타민82 항금 , 항문기] 대는 후유합위 소비기해 전면 하단 표기일까지 불고방베식사공품물 피하고용-숙소개 l안어 봉문이활 도는 |예 실온봇관 업소명 a [대_패렇물킬로로 17 영천시 소재지 [포장재적탤쪽 푹 '핑수 [품목보고번호7988055500812 알류 땅정 고등어 게 [r짚-- 료중하오0 화훈물 '때 지 합 포함) 조부외설다 분행 해물 의기 교환 는 "분움 심부퍼서 '힘습니다 박택망 및 "문개심다삶 그표 집고다' '객상님 '080-900-61331주 '푹부보? 고y 부덤 d Sajo cok '깨끗한 매모이 무리미금 깨애 기이기 부성 설리 시합 신고논;대 없이 1 3*9) VI 제주 [영양정보 UV터 7 9 345 기둥시어 대인 (UO W") 30 % 13 % 1파라 (회산면 혜목% 태위원회 우리치연 주의 서회 kcal 내표빌딩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영양정_ (생 ]양m권 오리지 식로"리가재유탕_리제 내용3당 소매분말 미국산) 옥수수전워옥수 괴국센다 가리 L S30mI (서르베야 등} 햄위말레이시이산) 번핸물 기능대유 양 589 맛메이스콤실탕 분말실물로 "'질조금 회기내출 액 탄수교물 대료명 (주 -말방렉속 상기포로스 가e럽 -내@스트 당류 59 (쉽jn하a %u동물액중국신 gi 이넷 다 휴@ 식이남요 " 최 대도요요 각지D -로비t확길학발유 지방 169 포장재질|프리프로하 트랜스지랑 스-[후면 끄기언까지 ~30 포화지방이 푹보고반? D-품-끔- @aim@@l금 그스템 또토늦 거 새우 계란 땅콩 맑고 오8어 단격집 239 ^동안 저품과 같은 시-어서 제소하고 아습내다하 가익 하어1다 [책장선올 피하고 시불히고 건소한 곳에 가념 무 바로 느심시오 "국덮어문 검은 청은 원료 중일부분으로 ! 드잡시오 '소비지기본번에 이기 교한 '1499 ";민없이 '불식늄 '"꿈년사및 신센5 유사a DWN 조개료신복 보진하십시오 Veoras '인심하다 '무해하오니 인제에 a 드망다 '인분해 rMO OVis A 신고논 '아보 U 구입한 농실 신소습신포심님 위대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C 드 l 4 770 애 식집유임 괴자 운림 IDaEDDKCaIED gX23지I) 몹시모장재집 [ 리프로 반품 및 교집장소 민기루민 미국산 소주신) 신망 옥수수진문_ 시르성유제기공유지다 멋r중말진하출 수@필유 불불양하이늄 아지유) 기공유지리어스데`화위다 '보관산 주의사장 스테야라위만리이시야신) 야지유} '해바라기유"손신-계-레오레진로조D력 이I입리E7 웬재규명 물렉용렉질십어지] 죄인전유스륙 워리이시이다 셋약-간_-일계지혜바라지 새우 되지고기 리세린국 라리시손레인신예스리트 성제수 손.제제q레오래진로 오징어 주머리 그리오래진세이지] 모도망 코로이분매먼다이시야신 53 네 트a 시청이서 표로 잎 469) 5.93 옆 옥수수진문 화물- 명장제; 평가제? 정제4 유r 인로제세 소비지기본 (보로 캐러인시템 레시린 Y 대투 구구) 보심해 소비기하 [ 9민 표기인까재비회인) 무보고런금 {9n60397D65-207 불]뀌다 우야 깨소인 미기밥 유:회사 / 강신도 원문 김외9 외리돌 그망이? 신고 유' 전문판매 길 5시시-주) / 인신밥의시 무B구 도마 U25 그 @ S 기 아 030o 93yo Auu E바</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드 식물운히 [과지 유저리제포) 소비기한 | 주어프기어가 예물히프밥록음,품맛 포장새실 |플리로록질런 [품렉출G런호 97604 87005105 전물트킬자치도 의신시 실동로P길 콤프들 로_ 지 주오리혼 세털@사용장 인도산 , 백설탕 스트츠 콤콤l%물발콤륭안유할#@지하g 우지 @l주주인E적플업등 유-워히시어}_햄워인유-물등시패속; 듭씨국양습3이스로 유화제 식울 [아스_림 펴출할라다 a위 ; 증잖m출자 _표고기 오징어 조캐로식활유 밑 발후유 대투 토마록 햇우 꽃 또f (출합 포해물용가둑_ 피려 잘훌끓록중앞-패지하 심고 위자 ? 불큰썹대입불 피해보상 '위해 콩기주입 방식물 사용히-습나다 빨리 드세요 부성 ' 불람시움 신고 원해가 불로 글예 본출이 동로 가급적 ' 1399 : 반문처 :본사 및 구입한 곳 ( 제품보오글 '직사관선올 국쁘없이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>'오리온 차 omON :권 이판 식n유에 소미기P @TI 모y고진 [프로다" [꿈로소고리 [03700075 제 부미 [업소염 " 소제지 | 주오리년 새사성무고임 P더구 어멘로 고9 (필스데야린유 말레이시야산 |. 과미드램배페립 러트입리 입가 (미 미국신) '/문 아가지롯로레인유 말리이시야산 가입유 ' 수수년말 신지분유 그야보말 회위가장#지전버스다-b리님석유 달려이시야신기^ 고퉁아버터 인도시야신 대시터 항원 뻔재표멩 코권하이) 식품 레시단 신고소점세 23, 캐피보답 참료 우무 U 사무 식요성유시 과다 유청문말, 재우 . 조개 뷰(군 h입 모합) 고리기능 소비지 기권번에 피한 피파보삼 '달걀 , 미원 소두; 나숨이 토마도 내시고기 시고기; #찌기 오징면; '무정 -당식명 신고" 국어없0 1399 , 반물치 - 군사 맛 구입# 리사장신닮 미개 온 " 슬물가 윗은 곳어 보다 개부 주 가르지 엘리 드서무 ` NUA 어이 틀 Diget '해 다이제 " Digeo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이미 Yung] H 버터팅 틈 버터팅 땅콩생_ puuer "#U미 49 #다 ) '땅콩생 버터롬 골드 2a" Gbolig 'Bull 명3이 검온 표기가 데 23입 땅콩산 WSID 여야) me 수거기 미규심) '내신 쇼 냄동합심워지 습주신 만레이시미 씩하다 오스트리야신' 4'R 손합심유,근것 산노(&gt;체 구오 사생심 ; 규카에 사라)-소 '연원반하새 요소제 계민 미고) 입기다 빠내 대바터 오시 해사리실 미히고 온도, 드기 'a 5없미 십51 긋대 wUI I 오의시 기닐 거어 더? 미래 c어스 예한과자 c어스 9lo 7선0 03 1소0 고소: TC 개타지자 (</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"801043" 03143 1" [품쪽명 매롭안맛 [식품유회과재유탕처리지히 "객분(말 미국산 호주산) 깜유(말레이 선분옥수수 외국산러시야 형가리 아등, 마 먹보이맛조미 문말 마늘추출울분말, 콤조렉룻딪소t외하다 고추표피리 똑똑미 미스트 설탕 정제소금 감자진문 '흉스다 [감로) 흔합제제한여 리비이즈 로건스로히 다누 도마도 쇠고기8 소비기 [훈면 표기일까지 포장재실이어마g [20010549541 -물3키미 "Y고닭고가 계란 땅콩 간용실터 전불 용합 모함) 출자용한 제품니 같안 '있줄니다 :직사장선울 사U?' {부관하심시오: 도보고번호 게 재우 미히고 서{하고 4'최고 ' 이;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{ G오리온 (-어가느메D 8 묶까 가리 8 의사시 미니 밑 '소재지] Ua '새규명 UIH ( 0' 9 미니 '하입어썩] 다이제 '파디 보관; '나늄포장되어 _ 물리-교 도장-질 진가온물 O로 I 식물유형 식물성우제안럽이U0다 . 전보부봉자치도 4Jys 제?임산금장 다o 'g례이시0 다이제로 금렉[배선당: R오리온 (합우 식흉성유지 미국산) , 산&lt; 조고그럽] '소망 오트크런자 [믿기' (밀 고코아분말 전치보유. 신랜드산) 진리문. Z0,8' 배설딩; 꿈국보 고번로 ] 헤이시이신) '대시고' '기입까지 근9예 . 각미스 $이 소미기한 5700 40 O80 4:S 근에 영양정보 'Cuy: S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I88 제르 다이제 소코 수민_ 기입숙시 업조럽 및 -호리온 세? 의신공장 신묵특길 곁 소재지 자치도 의산시 서동로 23길 11 옛말 다이제초홀렉[백설탕 식물성유지말레이시야산) 전지분휴(뉴 # 드산) 코코야분말 조크크럼] , 소트님판유 말레이시야산 판올렉입 말레이시야산_후치 호주산) '전립분 백설탕 당료가공 소비기한 [지골운 식물철컴림 산물완절 2 주석산 농후발요 26.05,22/16*43 무 올 제제[향 떠지훌증-스비기출로 27,05,21. (1) 가치 M료 밀웃유대두 신프 할표 기 179(604870053 곰 중아 토마토 돼지 손현가 소비다 ( 근예 커관 D80 U_ 5700 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UN3 s.구 7시: 방i" 입습 사다 U 네사 ' 신제 75 도라가0 137 새시 불다 식염 A우 신과 부성 고념 컬리 7궁 부 국예 보랜 숲; . 낮은 미배 @ 망려이시미심 '가코스터마_; 소미기신 (엔도니시다신 , Y응이지야산 싶노도 보코이버터 { 플렉인유 #미보말, '밀려이시야신 1;2리? 마기리 반표거 모 빠팅다 도: {퍽력유 국면하다 '미국신) 경시린 소거뷰, ~내로린유 보경시표 라R가3; 새집력예 코고이매 스 오심어 유정보대 바고기 도선요 ; '식고기; '어새"벼 '돼지고기 가뭄" '시복심유지 도마토 . 430 ';물가 - 미장; 줄사작 신설 CUNB DDE-</x:t>
+  </x:si>
   <x:si>
     <x:t>호실 OLoTE 크림키이리 -) LO포P즈 9 UUO 3000 dovvo 수 e 덥다 립 국신 '구 빵템 V 20 (73 : 785 이 쫓다 '예속 g원 09 }대하려 "T 물다 "#기 2650 9 n3엔 R8 : 얼 'i 가&gt; 'C럽 ZEG 제료 야채 ZEC 콩설 국내 wMIN MTT E꾸 롭 $a미구산 "E#모미신 '7가하 (싱가도로 '손갑식궁위7하유 '가5유자 '8익사3유제즌 {산도:성a521 ,eNBA; L: '가8R 제심가포로다 선보) _ 트y(가53지 , !R'S엿년다 &lt; FPa8 '기타고30133{ 'uy(y입 트 IYS(이= '을Y다 , 벼l 기다튼 :50 예;하 '요a 소시자 TV54; {기다가8E - ~#스U : '반39 '시:산 '1399 [y반5주수0C '/대 '패놓 기I '표싫이' 신고' X신 YV:N= '여장식다 '부y MSeuri Vu고기- Ci</x:t>
   </x:si>
   <x:si>
-    <x:t>train_20260614_134243_jpg.rf.70f5a394d6d4e8b7dbbc66c573e1ebfb_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134240_jpg.rf.a3472a2dbc06d03e25a793a45b56192b_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134219_jpg.rf.aee14c8a9786adfb8bd36d9e6b8e3711_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'발춘가공하터 36 &amp; 과자 ( OKa (도 WJull GaLIa l해 = In 비터동미 해 버터롬 골등 'uullo 2업 내H로대 해대 버터림곧드 6V 1.550 ' 8" 고심 ~22VCOSTI 소비기간 라국씨 식문유: [래오래진 스나근 깨규감 R'I {레인R'문하지이 음_다하로3_히이)야샌? 대스쉽 입성히코 아리비야럽. 지로델 밀기주 (비미국색) ; 소문울n도 던;) 유리제 'T제소터 입금저재 관5 붐내다 ' 미가신 '기공치' 기니기 {포집재지 교의 피뻐션집 입규 종터? 하' 27 고자m 미 매칭 햇 소재지대대제 잔 되는 고어 보과히여 진시모 및 교중님 키 구민신 및 습기신 미하이 표f이 t드 [함사E 신고히 국없미 사업 ; '합갑다 "무이 NWAACC시 개반 ? 심; 수신자 요a 뒷예 7과 # 제소시선 선 제스하적 만부니다 이 세금로 냉젊 신고기 사목민 보"과 O @;하다 어러 @ # dDDM AATA goy8기 N 1 예란과자 8 Gos 명화제 '그래: 누_비 GI7) r 애덧 b섯 806 5o;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뇌) 얘기 ^ m 2049 및 논 소비기화 제품 명 원회 설탕 소쇼톱 '유화제 피정 울 홀명 없아 '우지_ '프로 401 화 도당 기공버터 호소제 진주시 원 판대 권 대 용량 축머표기일까지 샌드에이스 우유크림 대면) 흘리프로필렉 스레 '소트님기기공유재하스테아린에스 과재유처리제물) 포장재집 식품유형 19820481021366 (레시린 d-토코폐물(흔합히] _ 유멩미국산) 부담 '기공유지 올레오레진로즈데리) 기타성탕(설탕 전 품목보고번호 밀기루멘미국산)} 기타기공품' 기타가공롭2 르회워관스테아린위만레이시야신))} 전일영 곡류기공품] 곡류기공품2 소트님3 마기린 '기공유크램유크램호주산)} '깜스테아린유 '텍스트린) 항료3 유s| 제품 (넣리핑올레인유 '연세우위원유국내산)) 핑유 '테아제 분) 손합식용유 k리제제요모주출문 '정제소금 건이다넘8 (@쇠고기 무유 대투 함유 판과정로 (항료] 항료2 어진모 ,이 산도조전제] [제미리심터 (조전적무미지 제신도조절세? ; h닐엉터) [해대세과식국쥐 723L 제조 {인길대로 유용전문 시나 신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dLU U" 파,다 ) 재요탕사 때 '제부역 내다 목수수진부 '기 기늘기위 형가리 '트럭미리 {외국산 소텔액 (원재료명 |안a니무차 직 발-원 적무썩쇠 '텍스트린 실요어대표요요스오백 포장질 소비기한 |후면 @문문요 j@om@@] 계란 땅콩 @돼지고 도미토 퇴과짓 게 '같은 @전보 공합 #함물 시용안 제품가 = S습니다 "시장_올 피하고 서늘하고 건소한 곳어 바로 느(시오 "간로 제금예 신문 간색에 | 검은새 '방화 U는원문인 요장어 흥미 일부분이로 ' 느썹오 소소기보내 의사 교원 비맛미 특징" '부성 불림식품 신가{ '비늄 년기넷 구입선 신뇨 ;시 신 형양정보 F7이a Px집) 깜씀밀내 "미과 맥분(빌 미국신) 세르비이 '외국센리시야 '플리인 ' (옥수수: 오6어퍼이스 (오징어유오징어 ! ,버티구이오징어맛시스님 오징어맛조데년 (오징어맛조미분말 카키오색소 [지주색고구미색소 [리"로보 고기일끼지 197 19/20154001 쇠고기 '시실어서거다 서구이맛 '보랜하su ''배" O77 '인닐에 '1399 최어언에 oay시l '6신:심다 어대 WBV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>162 9 남약 매주시 coN 밀 인 애 d 엿땅 98.7 % 청제소금식물 마 [원재료명크림액 부 도덤 수소암모는 데 (설탕 제 트 따안유 스 미 k 건_ 보관방법 대로 671 수대 '반 터 보관시 시 도 이 접실 (위#' 사 대 의기 이 (망 p' 이 ^ 내용량 고구마형기지 [과사(유탕처리제품) 제며명 경기도 (주)코스모스제과 (식품뉴영 960번길다 금강로 진접움 (옆하다 CSmnS (http llwWW 후면표기일까지 '판울래 캐나다)] 소비기한 '가루[밀(미국 '유표올레인유(말레이시야산)| 토코메물(혼합형)] 당류가공품 콩비터(인도네시야신 [명 Potmto 스타 '글리세라지방산에 물 '생어노로로제 '양파액기스CM 코고아블 스6; 말투 (간미 [뽑안 곳예 '바로 '리에터레(내 4113 11986033205148 OBo 국심상 치하 ? 실해 세a 구입지 주의시입 선쥐 기다 (기뻐 통</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|O|B-SOY|B-MILK|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|O|B-MILK|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>버터롬 CGDM 골 1p2 3 오 틀 [- 67 'Dultor @ 품 예 &gt; 월 # 때 7 |대 버터림 골드 1550 ( ' " j0 예란관자 r 열 ( 표# 몇 끝 예단지다 (올 캠 @ 탑 [ {다다 표 풀 V O 애응 @ { 틈 [ = ' 품 7 9G 표 품 96 물 Coes Ct</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03035 "료 (주산) 훌라t위 [절탕 혼합식용휴채종유호 @*로 교양산동) E]전관액국산 현내랜드산) 표코야분말 땅콩버 중로_p125 77 수 우재호주산 {미기라당워말레이지야찬_ 정제 도구하소 주심지오 밀가루 난백액 판스테야린유 @중"둑 530-리제소금 '기타가공품 유화제 정 스톱사 및 구입관 비타민B2 드니다 입유 HPC [런물조과 3 (하바라기유 유화제} 전문기공품 핑장제 유화서2 합료, 오자 우요n요 고기대무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대S Mg 장자지 나고번호 ji@ 문; 사주 주2공장 사소면 표륭로 "_로') 국 무리[러미터) 신도 {날?기다 시물무지 #콤플리 #e신동E WDVI 유다 171%) 당가고9 8 89599 일@깊수요심다 소__ 쥐-발 긍정하고30가Na다 0전어조개, 전물 3e 모램) 자틈입늄 국 또보가지 ; 불정 모불굽과물 S햇 _ 식움올 피하여 실로 보과 - 반물 켓 제즈입 '고프 a신터 (07O487-231 12 mII 8 B910 00 Gat DaE 소비 I OVu eVe 꼬리 DBL Owg0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>린0 말리 기타 댁린 힘유 @로움점일행 한천 '힘유제 조건제어모제베진로생승 %) (8959% l출 다요시설사트 일일길숲 플발콤플해탓 @혼고등 국번 M개류물전부 홍합 또 보심 가능 부덤 및 l사관신올 피하여 실문 텅각 '제조권 G5 산도조질제] P고"' '536 스고 {감미료) 식용유지가]품 산도조절제? 되지고기루송야 복숨이능-액 당알코올 171 D 말리돌 '알코올말터늄액 있습니다 '고등어계점; , "ui자kdy 모람) 잔 신고 교다 CtA 묻람식문 3311 반조 '고개지경센터 (070)4637 2023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유 UI Ou 709 대용량 D요 제품 명 샌드에이속 웃음크림 소기원 |불무_기인 지 유형 과재유처리지록 I 보고번로 회유 평유 I7 '대투보유 제 원 제 주 동물 매 리므 포장재집 쇼트망기공유재감스테이리 9820A8IO2ISS 375 유'미국신) '0 토코대지n히해 [밀기루멘미국신)) [레시린 ( 기타; gy 유회제; (올레오레진로주머래 재료명 귀(깜스테이린워만레이시야신)] _ !기타가공경] 기다가39? ! 우지 기공유지 들 a {마가린 : '기공유속램유그하다신_ '편스 테이린유= 곡류기공품] 곡류가공품2 소트Y3W '역시리83397 당리판오레인유 '연세우위원위국내산)] (호모주스문 프로테이제 (곤입식용유 '8 '정제소금 [지심로 { 콤합제제트 진구 기공버터; ( 쇠고기유유 (항료] 항료2 진주시 [ 도당 [미리식품주전묵L별자치도 [신도조전제) 호소제 [S비영다) (신도조절제2 2? 해태제과식품쥐 '한강대로 용신구 서S특변시 트 움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Digey Diged 83 Uo3 Diget( 간 식문유성 바사( 새추원 '하사버민 오리온 점심 업 떠 매 남' 밀암시 심히/ '노/문 만때 소재사 원 (쥐오리온 서물시 평산 구 백범로 90다길_ [제기해로면"기원-지 [_명혹분(옥수수 호주산 백색 ,식물성유제금올렉인유 말려이 탑 시야건; 채중유 호주산) 닭강정소스 외국새미국산; 미국산 중국 )외국신(인도산 M, 사과농축최v액; 닮근 수S9 (축액; 발표식초] , 기분 둘다 (n시주엉드라이드치_무#배다 V38 떠 '국내산) , 닭고기 |분말(치증껏 인도네시야산; 부음참깨 밑 대투 도미도, 내우 합유 불리예트랜 (문목보고번호 무유 망점 오침이 게; 야) 리' 4 디어M 농 Y끼사 (토마드O적도마토 아미노산농추댁 중국산))}, 파인애들주스 치간맛 국내신}; 뒤고기 구운선일염 (국내산) . 뒤고가 '최고기 [4장새진 12018060302319 }5이 {새{다. 민족 , 5' '고축어 고기 2026 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RABO Grlpeftur 하리보 자목 책리 100 ((310 R J 의세 1 메께지 1333 하업 썰리사 설기다 399 공지밥다 새개길 70 "21578 _ 더시F 어신 무바무신 제기 주드시관 구민 '심합로 엘어베리 엉입경보 UBfime 33 UB BMMII  (U법 내5;   IOmng 급수되다 B70 입위 답; 0 지붕 Og 가리 Vg Us 0g (BOTu GNA A OI 0s 0s "0016 탑 바입니 차8? 거거런드 n Com harlbo NWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UU F 셈 외28고 넷애 인5 없이 집$ [바비체터 소콜러껏 후 K#a부도로 어거드t시햇로 4흉y-버{ 기입까지 무고런오 {영양장보 V추ig lial 제기 치피 {경가트 직임 정주시 `구 _로l 뜨집 미로 {진; 주월 T유-팔출로움 전문유 발a로적= 톤출히 4 미실팀 T기 -무E비럽물_하-_형 망플리 핑: (h물-턱자 팀주-물 비출님신: 식- 표로문t '가공유자 봉 (방고 분말유_ 소르  단자훨신 사리- 기터호움 스_톱 미0 U스리훨신 플로등스 진경 빚 {37j5P7 0Z3" 청트 백 감유 담 대지터 구교; 팔발: 유뜨로 쇠끼 고사( [지하 사과v 비교교t 빨- 퓨문기오자월 신 흑p 대 HACCP 두중5하다양x8 보l Z 곳 피온 커회국 한고 타스템SO '리 DAIa EWNIs DD 오기다 '부드움] I전만 {의D쉬리( '있다 I6i '방고 생명" ImD [mmMmm 플리하 만리맛 [사훨 소비 식 정요제 '매기지하신 . '발히-@오 돌레다지훨진  기루"다 '일현세 년문 전배] 퇴지부유 | [캠어터리D-스리돌 신드조절계경 스물장우지다 "뱉버V-기" '출서린 '글리리지림산-스르 (농소무해 비 트스템 | 본림히자기번 '본텔적U스물성으자 내_놈-분말 ,돼짓  영리 제로 방로j품 퍼러스 _바로회직식화 [[입거등 스썹제제식물성유자 계 제릭국 'UiJsr '80TTT7: [다? 숨기  은 l신물</x:t>
+    <x:t>으3 어x b' 양' 훌중통연 공 학물하영 88양 : 국% 50 8중 5 x연하@ 33히5 '훈업) 동두) r연두 G호 어머고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀|대두|우유|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대두|우유|함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대두, 우유 함유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O|O|O|O|O|O</x:t>
   </x:si>
   <x:si>
     <x:t>용세의 35버i생인 Gni 농빛 Orone 용 LOTT 1952 E내a내교레교 ESnP 퀴T [지발 재조판매인 '켓가필문 '선탕 코 늘틱 11m5 '유표움;가궁무자-거WE 국신) @대타유유 88 % 합심 남비 '구멍 심심 말 예반 03 % 곳예 진 무: '깨내 보심 시한반 '반집이 생길 수 8 "801062' 및 #없이 녹아 히안 교민 유n 춤 '신고트 국 없이 }리늄 버문 미a '부점; 고문 마련 만 가능 유지 하 k입 제료 실이I IIUI 10o VO (영양정보 (10030306010121 {리프로-데 경기대로 진위면 '미국신 전멋 식도 법그럭 핑버시 #기인까지언 김기도 '11 920 k데랜무드(주) ` '코야분밥| 인기리밥 '딱스테다리R업 소비기 '곤함문유; (끝분변유 n유 그데스U다 R1미국신) , 소드님) (기공유지 '메y미로) 골렉기공유세싱가포고산 , 식즌유임 손입분유] 0-소비터 '?함식용유(경화유) { (정제수 합요끓} {전리객 {정비소금 손함분유유그레국내신 , {인재료임 (선탕; 가공유재싱가꾸른산) , 신M 쇼드님(기3유지; {유청단내분마 신5조 심제23, {유Y미 '기타선틱(실탕 전분) '기타코 코아가공품 플래인유) , '기타가공품 주정0 '본사계서 고남지원5터 유라세2중 변질감은 드시도 무대하다 '인헤예 '청류주0 있의u "8c26 의합 피배 '소비자기본번예 습기루 '식사관선 ' 1399 조|릿 붙람식협 '뻔심습니다: 돼지고기 { #]_자다 ZEC 야채 야채</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이미 Yung] H 버터팅 틈 버터팅 땅콩생_ puuer "#U미 49 #다 ) '땅콩생 버터롬 골드 2a" Gbolig 'Bull 명3이 검온 표기가 데 23입 땅콩산 WSID 여야) me 수거기 미규심) '내신 쇼 냄동합심워지 습주신 만레이시미 씩하다 오스트리야신' 4'R 손합심유,근것 산노(&gt;체 구오 사생심 ; 규카에 사라)-소 '연원반하새 요소제 계민 미고) 입기다 빠내 대바터 오시 해사리실 미히고 온도, 드기 'a 5없미 십51 긋대 wUI I 오의시 기닐 거어 더? 미래 c어스 예한과자 c어스 9lo 7선0 03 1소0 고소: TC 개타지자 (</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소무다 HPC 03f)395 듭 @ 괴롭트T::로로} 탈물로고동 l투잔출월플유네달랍등) na @부망 또균] 고 [출플로픽록유-바S롭l옮하로이_양무페 수 [수제호주선 해바라기유 팔스테아린유 3오본길 [말가루 단백대 전문가공품 기타가공품 하여 주십지오 (제소금 평창제 유화제2 항료 비타민B2 자 '요금두렉030 리 스본사 뜻 무입한 귀 B요라마 시고기대무 입원 7니다 유유 흥체적위로 당콩: 유화째 유화제] 정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오': 6 입sA0 HLal "땅콩샌드 가루고 버VP 2불입 ( V다 립하하| IVp] |54 R도VJg개 이미 ' 400 ' ' CROMI 심 0 'R9 오 8 V 5 ' 어스 8 소 e 예 2 @ ' 8 예로 '대 $ J 용 d 중연 오 손 3 망 2 9 군 개I % 틈 뜰 중 동 호 틀 돈 뿐 퍽 출 뿐 8 도 틀 옆 출 틈 품 터 # 3 원 틈 출 sG31 739 C '움 명 류 물 영 별 톤 품</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|달걀|우유|대두|토마토|쇠고기|오징어|조개류(굴)|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐디뱀내하항 50 "훨8 ll음로 무중입지올유화 /물t 구1 [유등런문 -대인 (주크리운제과 전북자빌자지도 군섭 서주무드주P공질 소비기인 후면 표기일까지 짙리 소비션 땅 물없 올리고당; '중아놈 -데? 항되복숨이 #감미되 현 신도조절제 _ 산동중질 고전행) 기타스용우-기 필중야 소 불중이용3 똑중아항 ; [지고기 복승하학 버리주스 유화재 달걀 호두 밀 햇밀 영콩 4 J물움움유 망6어고기 록말록지증-콤무양 [률이용고 [한P5고기 오정어 엇기루다_ 조식 신불피하영 온도 [그시설서 저조하고 있습니다: '드십시오 패보전해 주요고 봉후 가급적리 및 영업_ 물은 의만 피해보상 교환 및 반품 론사고객앉다히말 고객상담실 엎출품 {@주 @  표꿈 과랑 부정 운n직품 진고는 국번없이  O 내용립 50 01 160 kcall 27 2017048457793 품목보 고 '고등어고지의 표기 7도 소비다 담080-109 섭저지 '안속니다 26 2 움망점보 WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O|O|O|O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위시로로 입" 제2 우지 및 밥표 3y' 큰o 게; 대내 재우 4y 대두 빨리뷰 부 개본 설 위해 뱀 군 EI 늙론 GrOaTN 소비기한 마지(운처리제a 도장재집| 식품유형 볶음양교맛 전북특드자치도 [고래밥 19760487005105 인도9 제문명 의신공장 알따옥수수문말 (옥수수 '부움양넘다시스 품목보고번호 R오리온 호주산 ;화다 변성전분 '바메규양님-이스무` 소재지 말레이시야산 미국산) , 업소명 [밀가루(밀 판율레인유 전문 식물성유지 원재료명 말레이시야산, 함유)) , 괜료(a) 아스파람(메널알라년 불화조미식품 소개주3다 (판유 호집어` Jdn 쇠고기 기본범쎄 산도조점제 토마토 'm고기 소비사 새요 '돼지고기; 갈습 사용하엿 습니다 _ 우유 '가타색 목숨이 털걀 호두 '방식롬 땅정 보권 공기주입 구입다 '국예 낮문 습노가 본사 반표처 399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VV VUU 이기'신) I0I2 미시7 [모강깨신 [ionyo'''oa12? 메미 안침 내기고기 고기 오집이 소개; 모양) 싶사인기다 눈생대 거교 나 보심계 있,니 반 " 물강소 수입시 넷 고개g다 플시적히실# - 화심터 고개상되다 080 '900-6133주 '뜨거;니 부다) dsajocoki 깨소신 예구 깨끗이 우리바늄 깨야 이사 UI) 부성 불림 시멘 신고는 국장 없이 1399) 새미이" 오다 | ?래인{m도리 UnMI 기래하인히 {불보사고넷; 우리지다 주이서:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESEALABLE OPENANDRESEALAT CLICKSTRIP Shiiies) S 59 영입청보 480 Kc3 스스의자) 내요딩 ID '비닐규 48g텅 가로시 요 쪽부_@ 톤듭@ mm OTHER 나주이다 FEIIO로 점정지문 대스리 프똑O다 5낌 한신심리트 } 기니무히 4405 호 미라 이루 '미로 {이규 향 #해 -하3 | 훨신지: 중국 출 푹</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{ G오리온 (-어가느메D 8 묶까 가리 8 의사시 미니 밑 '소재지] Ua '새규명 UIH ( 0' 9 미니 '하입어썩] 다이제 '파디 보관; '나늄포장되어 _ 물리-교 도장-질 진가온물 O로 I 식물유형 식물성우제안럽이U0다 . 전보부봉자치도 4Jys 제?임산금장 다o 'g례이시0 다이제로 금렉[배선당: R오리온 (합우 식흉성유지 미국산) , 산&lt; 조고그럽] '소망 오트크런자 [믿기' (밀 고코아분말 전치보유. 신랜드산) 진리문. Z0,8' 배설딩; 꿈국보 고번로 ] 헤이시이신) '대시고' '기입까지 근9예 . 각미스 $이 소미기한 5700 40 O80 4:S 근에 영양정보 'Cuy: S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UN3 s.구 7시: 방i" 입습 사다 U 네사 ' 신제 75 도라가0 137 새시 불다 식염 A우 신과 부성 고념 컬리 7궁 부 국예 보랜 숲; . 낮은 미배 @ 망려이시미심 '가코스터마_; 소미기신 (엔도니시다신 , Y응이지야산 싶노도 보코이버터 { 플렉인유 #미보말, '밀려이시야신 1;2리? 마기리 반표거 모 빠팅다 도: {퍽력유 국면하다 '미국신) 경시린 소거뷰, ~내로린유 보경시표 라R가3; 새집력예 코고이매 스 오심어 유정보대 바고기 도선요 ; '식고기; '어새"벼 '돼지고기 가뭄" '시복심유지 도마토 . 430 ';물가 - 미장; 줄사작 신설 CUNB DDE-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7 4 h진 무 너대 ; [활@ 2 "주려주스 중행 9 '유유하 잔 용 이 지온 '오. 제 70 오 'T 개용 곳대 보관해 모생 F ' [ 내기보상 바고 그_품신교 ( [명양청보 160 MI 7 I 낱p필 욕 문미 1339가) 유 계 "Vun s 7무보: 9a히) 설다 포기의 신망다 '맨 (소바기다 '올리고  "신도조실? 'ga안 '산도조질제 ` '"중 거i 보 k료 "복숨083 [감이회 : '복숨082 '물잘오다 '유 도모 '피하다 폐고기도 {조리국튼 5오 직량 살이다- ; 가_ 매_OL 시용산무 [제조하고 ' 자조시서 (주시고 '(서용979 은 '7 경식품 내끝니 377 KCI 새</x:t>
-  </x:si>
-  <x:si>
-    <x:t>I88 제르 다이제 소코 수민_ 기입숙시 업조럽 및 -호리온 세? 의신공장 신묵특길 곁 소재지 자치도 의산시 서동로 23길 11 옛말 다이제초홀렉[백설탕 식물성유지말레이시야산) 전지분휴(뉴 # 드산) 코코야분말 조크크럼] , 소트님판유 말레이시야산 판올렉입 말레이시야산_후치 호주산) '전립분 백설탕 당료가공 소비기한 [지골운 식물철컴림 산물완절 2 주석산 농후발요 26.05,22/16*43 무 올 제제[향 떠지훌증-스비기출로 27,05,21. (1) 가치 M료 밀웃유대두 신프 할표 기 179(604870053 곰 중아 토마토 돼지 손현가 소비다 ( 근예 커관 D80 U_ 5700 6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANUA) Gapnsaiyes} 터시 매596 내륙화 1000 연인정보 304 태시고기 IIO) T? TILY 0029 -:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>open 중 a 굶 i @ 낙 고 옆 사 '7 유 야 팩 7 출 모 탓 푹 못 # 무 흙 뼈 틈 초고y 품 조집 무기 Chd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시5 'Ue 에너지바 N 백런스 ULIHIIIII 대다꺼N지 Post 에너 교 에너 의부 0) IV mImm " 100 어39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오리근 '합입예속 ! 들어가는 미니사이즈 미니 나늄포장되어 보관 휴대가 가프 제품명 다이제 미니 식품유형 | 조홀[가공품 포장재질 | 플리프로필렌 업소명 뜻 소재지| R오리혼 제2의산공장 전물특별자치- 의산시 설동로 23길 기 원재울히 ] 밀가루 (말 미국산) , 다이제조국랫[백설탕 식물성유지말레이시야살) 전장 플유두질랜드산) '불고이큰말; 조로크럼] 식물-용지금유 말레이시야산; 팔플레인움 플라이시야산 백설탕 전립분 전지분유 오트-런지 잔드조증제 공종 말-사관 산 밀구츠 코크럼 후유 대도 학유 소비기한 | 즉면주기일까지 품목보고번호 [ 19760487005157 발품들 물루 특출이 통하듣- 팬집_기 최퓨- 품고- 옷며어 문해 # 조커로 꿀 발문함) 혼일가등 주퍼지 길국국에 인런 걱행 보활: -원 셋살홀컴출i해용 1399 가 낮르' 국데 보관 '개공루 가급증 뿌리 들서온 부정 반문치 본사 및 구입인 고객센터 {화) 080 '023-5700 (문자) 1522-4002 영양정보 중 내용밤 80 8(40 g X 2봉지) / 1롭지(40 인당 197 kcal 나르급 Z0) 10 % 민수화: 26 8 *| 남류 DDE 10 In요 17 % 랜스시밥 U, 무라지 고보 40 제밤 오;ng미만' % 나때 식 59 플레스레: "맨 생망하 7: a내 대욱 UA 7 (MM) (주오리c HACCD atTt '80 905 파이제 중 c dSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J론풍 E: 글느; I8 9r Z9 겨y C 터거 803보 09goo 268/C @기0I60U n리 IA 091 Grrg Ge 서구하4"38531 8스경= 269</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그회 어리거 S 느 P어 영0 보 UBV 600 268 088818 ' 기;이다 Smo O뇨 NS 0a 스지다 09 09 OmnO 57 uo 4653 VeoI UJizw OL 5332 Anlae Cad :어9s</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥스다 K 09 이 mI [H 소 O 이 (O 6 거개  기) 25까지 2026, N리INa WN '제Iila GM 입소입 기인N 소새N Ved OOaliBokCa '(0EN 'io 109 없새요버 06 'Noll</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설탕|포도당시럽|팜유|구연산|덱스트린|변성전분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-SOY|O|O|B-EGG|O|B-WHEAT|O|B-PEANUT|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(ARUBO) Ii " li "MI-S 하리보 프루티부시 두미주 이 바리보 아S 꼬다' 10D KCal) 메 개민 표사점 #이싸기 바가다 는 리 3중프리지 78 시 02-5/8-0385 17연신 "5 시대 V3 M입 끼0 Gerivo) W0O p 가꾸다 WOOI디 자고기 이터 '01340 '김기5 새꺼거 곤미입 '376(2 '리0 N햇 Doroso yorttoo WWW 닫;^</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'오리온 차 omON :권 이판 식n유에 소미기P @TI 모y고진 [프로다" [꿈로소고리 [03700075 제 부미 [업소염 " 소제지 | 주오리년 새사성무고임 P더구 어멘로 고9 (필스데야린유 말레이시야산 |. 과미드램배페립 러트입리 입가 (미 미국신) '/문 아가지롯로레인유 말리이시야산 가입유 ' 수수년말 신지분유 그야보말 회위가장#지전버스다-b리님석유 달려이시야신기^ 고퉁아버터 인도시야신 대시터 항원 뻔재표멩 코권하이) 식품 레시단 신고소점세 23, 캐피보답 참료 우무 U 사무 식요성유시 과다 유청문말, 재우 . 조개 뷰(군 h입 모합) 고리기능 소비지 기권번에 피한 피파보삼 '달걀 , 미원 소두; 나숨이 토마도 내시고기 시고기; #찌기 오징면; '무정 -당식명 신고" 국어없0 1399 , 반물치 - 군사 맛 구입# 리사장신닮 미개 온 " 슬물가 윗은 곳어 보다 개부 주 가르지 엘리 드서무 ` NUA 어이 틀 Diget '해 다이제 " Digeo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|달걀|우유|대두|복숭아|돼지고기|쇠고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-MILK|B-SOY|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 대두, 우유, 땅콩, 달걀, 쇠고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>k'세곰 나의티타임 달린미 E입 소자 슈* 함께 튼튼안다 '위만 휴세 @hocl?3 CSOSOO m P리 [모집지심다리 UO무리 330 1각터 기소치루 대한 79표7 (사시1 서로 '신지분위-지나드썹) 오 히가긴 리 코선이버 신어 의' 아예 미계 피내부 느세요 장'" 메이트 커뻐; po트 '이침까지 요골 FZSU-ITI DS 영양장보 {식찮미 a하: 바가 Igt6Dsatoo'u7 신국보 고번소 ~"리산-김 식8생유시만다이시야신) 주오리 보수3보 쇠지 @ 신비서20 '그O베다 용 A l6o</x:t>
-  </x:si>
-  <x:si>
-    <x:t>린0 말리 기타 댁린 힘유 @로움점일행 한천 '힘유제 조건제어모제베진로생승 %) (8959% l출 다요시설사트 일일길숲 플발콤플해탓 @혼고등 국번 M개류물전부 홍합 또 보심 가능 부덤 및 l사관신올 피하여 실문 텅각 '제조권 G5 산도조질제] P고"' '536 스고 {감미료) 식용유지가]품 산도조절제? 되지고기루송야 복숨이능-액 당알코올 171 D 말리돌 '알코올말터늄액  있습니다 '고등어계점; , "ui자kdy 모람) 잔 신고 교다 CtA 묻람식문 3311 반조 '고개지경센터 (070)4637 2023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>@ 아도: 이리덕 @움 눈씨니 얼굴 #Q로 가꾸_a P  내gD Ii0 Io9 1당류022 U2pral 미0D시 08 TU 2DNC @_이멘로 runrorhoulCo Ld '수입원 신n로 'NA'</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-EGG|B-MILK|B-SOY|O|O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|대두|쇠고기|토마토|달걀|호두|밀|메밀|땅콩|고등어|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 달걀, 우유, 대두, 복숭아, 돼지고기, 쇠고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>labels</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>인식 불가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O|O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tokens</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C' o0- 도 Blenc Cr 산도 깊은 '불런드 새빵 커미 내용 ;"요| 맨맨7 "Ay 이미국심 시답 사다 0 대무구 0 10 "0o답 왜7 소들기물 '"랜-그리{ 담기 비다 럽나위 '93 '언제 브대 나두유 무리다 방' 신문 '입82s ID 벤시터 42 고함 미 반물 시고기; 햇i 본사 책미 V '주터 리시오 덮 ` 진임음수 d9 구입런 소비자3 예 또보트이금보 0 의반 내 보심 신과 F메 (서3 V 버II VM TI 디y '가사T다이 31 Y다 8: TC 29 RUASTING  GOFH 풍미의 바섯 시그니처 '이미지예 (운산' FEI 기심;임 며자 나오 IDV3IG5I "심새생 소비기인 g리BaI지_P CPn Y새Lw [가이인 드움째 영양정보 유끼 소재새 '대인터 [선생요시 [민드마루다 (알레이시야신) ug:' 비R 신어서로 @소자덧 세O스 P 기비터리 예스내e (너_=국신)) 어징래 p재기끔 P외유 iCal 가,재; '기다기공히 {아H이N야신) 그) "중어제제스비다 "드바켓자 그다자' JAL 유자 , 산도츠 니 언드 'Q어스보 a 아스기보이지적 재심국기피므두 '해다F Rl요요 P리어스; '리싸리 FPA '모라리신6다 Rr s {어디오피야신 자; 대기가 유어자금다 '밑가  '-N3다 그거하다 '피의고 NSCTII 모시 53 V시  모아지대S '구u움이 '고재상미실: Wco? (수신사요주부 V7I TBUI UD' '년N)- IUP 8882</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유, 대두, 쇠고기, 토마토, 달걀, 호두, 밀, 메밀, 땅콩, 고등어 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Salmif Canoylngieo desloseau and iarnkmt  manos Sugar; 3neni dmount0 u % Podu Mah NTavill Erin 영입경보 659 U망 0g 소고기 OR SAVAA 바이 c 0o시 USO 스_쏘 'horibo WWWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CKOWN TI Sigran&amp; 도 RUlBIlRGCOIII 기으 끓미의 F 플 바x시니처 불런드 운산 C( 앞영 이미N에 너거린 219 8" 소I 소비기신 만기_끼기 엉양정보 NU N뇌 37 kcal 그스 커피 미(지t기이 "미 ""새" '리n '시다 '미7대 고기 미과 I09팀 가스L ATAIISI 소속 '증기 대무구 신@-T" "7 " 소끼시 {w리이지이신 ,미a 무 나SU IWmn M키만 마르다' 계자 ;재끗자품-a 자? UUI 고녀이시다신 'n)lt 6비 [n대 기터가리히 _가계 시미 d점9 틈 플_패손t # 어리오리야산 m0  무하자 언제 NUn 가미 어기뻐터 가모니지 'V2d ToI 다스지다하7 잎: 피지:2u 시교 입사 @ 7색   ? 고요두문  y인소 스모 구입나 FL신 휴 깨어고 9 나으; Be9 되-꽤어 왜 U UI 뇌' 신a 비리Oln) '인 어고하다 [라s '내 이다 IX II '거W) 쿠르다스 커피 Olend 3eA Ue 가괜리{ # -가 ITI ( 7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134633_jpg.rf.327ec502b3f860d4541a47a28709c5ad_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134642_jpg.rf.87d0fdc89cb54a0c5e18a92dfc97d4f4_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134646_jpg.rf.452fe6dc8181636d862e74e1b949ebc8_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134709_jpg.rf.97d83ad01aabec6bec873aaf8bada61e_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134717_jpg.rf.edbc6f1413bc42d5dfeeac027b17ee89_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134343_jpg.rf.b355ae002b7cb468768f213dbacca279_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134401_jpg.rf.3d9bd20ccf494a7aa3ae8dcc32fb1f7d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134405_jpg.rf.95f755a58c8b6cf0b264befa51185eac_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134417_jpg.rf.6c87b434b730b69faf7c535b85711c38_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134713_jpg.rf.14f7b250dd0697ed26398ceec5e9e176_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134628_jpg.rf.8af5ece5fd8330cdc2d0d3faaabf1a03_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134347_jpg.rf.baceb8a8302550ff7b5b772780f96d25_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134351_jpg.rf.e7f3169faaf7fb813f2beb1cafb5b28e_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50 5 제1  (국색스 Ne 밀 우유 대륙 [소비기화 |말런 또기히하집물표보고a IIYAMOe 포장재질|몰리프로필로내포장면 해태제과식품(주) / 천안2공장 (제 조원 |중법 천요스 지률- |울 n@호 [유통전문 올림언해대짚구 [길 기히하다 '용신구 컬리다 [판 매 원 및 '본 미벼 '38* #8 곳 *이 '생격 주 내내' '하안 7 k 소골되다 벌스가' 사사)  주 스틱 NKy {관틱 [제품명 [포키 극세식품유다 조골렉가공품 [원재료명 및 '당 코코아매스데덜관드산) 가공유제성가교로산  합량 | [밀가루밀호주산 소트님 떠gP 코코아버터; W? '미국신 Sv '정제소금. 유화제2 흔합제제치자황색소 유화제] '항금 8대터 산도조절제2 효모 호소제 정제수 프로미 하&amp; 이황산류 한강대로 서울특별시  충륭이 서늘히고 피하여 습기찬 곳을 '공성거대워원화  세물은 직사광선 ((KU ` '요금부럼 ( 주십시오 '수신자 보관하여 W '고객만족실: '국번없이 곳에 N3r 도미도] 피해보상 신고는 '세중온 '불랑식품 = (의거 힘으나 '있습니다 ` '부정' 구입한 '세조하고 보다하스 6677) ' #년송이 . 'U이하로 보사 및 I석예서 불하이터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-SOY|B-MILK|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-SOY|B-MILK|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|우유|대두|쇠고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 대두, 우유 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 우유, 대두, 쇠고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|대두|밀|쇠고기|달걀|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 계란, 우유, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 쇠고기, 우유, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유, 대두, 밀, 쇠고기, 달걀 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|대두|우유|땅콩|달걀|쇠고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-WHEAT|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-MILK|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라pa;^ 소컷끼이 5I 가 IS 5 I AIil 98na4드새} Ooh 조미기 149 김수시하다? '오리온 (주공장 비림 주 스지 둘멋 학수 '3중 식S i집망고 '식물' 발들T스트레 음@ 말 구언산  "필말 대로 텅 구모저 해j 방움 흉업떼= 재후 개 1399 부정 "l 릭=트 평콩; 의한 불로기통 '책장 둘하올다 곳 본사말 '반문치' WI 망고리싸다? 구 { 1ena 8 SUI 어씨 8베5 경정보 I0m 가너U)기 모심재심 '식3청으치다 직출유교 | 밀리  사가" {립불/인요 효심복도 '밀리미시야산; '근래 소비담유 또도망 요거트분길, 0-소비물먹 물치로유 소르비단지방산-스크리 산도조전제 전끗 '예트님신 ; 문말유크림 #E미3 물린 상우지2 {방산계스템로 백설탕; 국N고기 '이스라결산 온함제제키변성전문 , 성문사 물리리지등 'S입제-3식물 (농춧무데' '꽂로필런리룹 '비져나농죽분등 행료제제방료 집입가등 '비라물태 Biiy HO '-카로켓칙색로 초료출 'Biim [0리비야켓 'z없이 (혼합제체식물성유자 9요 오징업 '불랑식품 닮고기 토미토 '피해보상 호두 '기본번에 "습도가 낮은 소비자 511253 - Ioym   c-등c장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|우유|대두|땅콩|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|대두|계란|우유|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기, 복숭아 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기|토마토|복숭아|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 우유, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유, 밀, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>corrected_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>quality_label</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|우유|대두|아황산류|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-SOY|B-MILK|B-PEANUT|B-EGG|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드 식물운히 [과지 유저리제포) 소비기한 | 주어프기어가 예물히프밥록음,품맛 포장새실 |플리로록질런 [품렉출G런호 97604 87005105 전물트킬자치도 의신시 실동로P길 콤프들 로_ 지 주오리혼 세털@사용장 인도산 , 백설탕 스트츠 콤콤l%물발콤륭안유할#@지하g 우지 @l주주인E적플업등 유-워히시어}_햄워인유-물등시패속; 듭씨국양습3이스로 유화제 식울 [아스_림 펴출할라다 a위 ; 증잖m출자 _표고기 오징어 조캐로식활유 밑 발후유 대투 토마록 햇우 꽃 또f (출합 포해물용가둑_ 피려 잘훌끓록중앞-패지하 심고 위자 ? 불큰썹대입불 피해보상 '위해 콩기주입 방식물 사용히-습나다 빨리 드세요 부성 ' 불람시움 신고 원해가 불로 글예 본출이 동로 가급적 ' 1399 : 반문처 :본사 및 구입한 곳 ( 제품보오글 '직사관선올 국쁘없이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|달걀|우유|대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0 @ 1' ; 그_ 814973"6u 319 도 S찌문- h미다 oouinc 무 4Ol Ke) 소입스 4보 숙r_ ) 장유자3E 이디 유지유 비사스 표망사다 아리베이터 닭 96 IW '0J버7 On' F_E @ER보O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{ 출 환통 EIDSICal [원질보 IIV 틀 Vu 70 42 운안: - ; 7 { 틈 통 총 = 흙 = 총 [ 도 틀 OEH 출 비"g] u v';NA 터t:] 구 c6 " 부벼 V'a otovo 무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-SOY|B-WHEAT|O|B-EGG|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아리보 드어린 여3,정다 세 M표8 일, 우유m '@안 제 기은 세조시 Y예서 메조히고 미l니다 J268 kcal) 라드 긍성거래히 언쥐 교사 모생대리 기본어 이거 표시적의 | 실꺼기 '면 맡T 수 ^ 3나 기 무껑 김 식8 신고' 겁가노 국두 하이 1399 제3 내 입쓰덩어리가 간국실 70 '권립 수 있으u 미는 제즈? 9예 검계수 서 사용다 식장터분이 군어&lt; 구업 으도 인사예 유해하니 제거 $ 바거로연 영입U보 u83 800 268) Ug급딩 |말 @입 청_ 기O내 다르 @수의요 627 고기 도이도 목숨이 입 에 지반 Oa 3UA 트대 N멘 0 모화시망 0 Omio '50 Ue [표 113055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134914_jpg.rf.7cee80a5db824002c096a87e82813a54_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134727_jpg.rf.a578b1bf67f08e0aab4d7d5adafbb5a8_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134736_jpg.rf.03a2493adcbaa0d016790bc19865b1ce_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134746_jpg.rf.7d1a7cd82aa48c73d4ec530cbdac8bcb_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134906_jpg.rf.0ad513d152b43592df5b1a127986367a_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134731_jpg.rf.2d9c0647831288fa80bdce9448caaef2_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134903_jpg.rf.3d5b95d8da7b6d2e8339eba1c797c43d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134822_jpg.rf.6262b41eb47cd6c2a3822e89e46e4dd0_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134849_jpg.rf.b34bfd20083649cde5b04fb36cb8010e_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134815_jpg.rf.67e5a1f020ef1497e57ca19281cf0a5b_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134835_jpg.rf.5e6d47619c65a4ce05e7463f1a19ff67_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134851_jpg.rf.ac5b8260ed1b605528c81736dcdbbb49_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134753_jpg.rf.15ac27dc4ca10f457820a91f4c092b6d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134806_jpg.rf.bbeca6756c7042e21136edfd37395545_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134837_jpg.rf.ed4d94df21a4396911884068a76f69cb_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134825_jpg.rf.fc0da97da2e2f3ac418e3956ebbdbb9b_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134845_jpg.rf.8fde562ca1a108fa765b02fd8f8d47f4_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134813_jpg.rf.517885023019c99bc7e7c403b8a1c62f_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83 구끔자 깊심 산 코어마터 기에익 맘계 버비I k기 '바MZ요표미티진터 Ti다 U생 Da 주껍무서 "조키a 입기 2.160 ' g80 3 시이산 {가가라 Yer" '텍스데) 유1'오 '다기급R yy; Ln SIXITEIIRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용세의 35버i생인 Gni 농빛 Orone 용 LOTT 1952 E내a내교레교 ESnP 퀴T [지발 재조판매인 '켓가필문 '선탕 코 늘틱 11m5 '유표움;가궁무자-거WE 국신) @대타유유 88 % 합심 남비 '구멍 심심 말 예반 03 % 곳예 진 무:  '깨내 보심 시한반 '반집이 생길 수 8 "801062' 및 #없이 녹아 히안 교민 유n 춤 '신고트 국 없이 }리늄 버문 미a '부점; 고문 마련 만 가능 유지 하 k입 제료 실이I IIUI 10o VO (영양정보 (10030306010121 {리프로-데 경기대로 진위면 '미국신 전멋 식도 법그럭 핑버시 #기인까지언 김기도 '11 920 k데랜무드(주) ` '코야분밥| 인기리밥 '딱스테다리R업 소비기 '곤함문유; (끝분변유 n유 그데스U다 R1미국신) , 소드님) (기공유지 '메y미로) 골렉기공유세싱가포고산 , 식즌유임 손입분유]  0-소비터 '?함식용유(경화유) { (정제수 합요끓} {전리객 {정비소금 손함분유유그레국내신 , {인재료임 (선탕; 가공유재싱가꾸른산) , 신M 쇼드님(기3유지; {유청단내분마 신5조 심제23, {유Y미 '기타선틱(실탕 전분) '기타코 코아가공품 플래인유) , '기타가공품 주정0  '본사계서 고남지원5터 유라세2중 변질감은 드시도 무대하다 '인헤예 '청류주0 있의u "8c26 의합 피배 '소비자기본번예 습기루 '식사관선 ' 1399 조|릿 붙람식협 '뻔심습니다: 돼지고기 { #]_자다 ZEC 야채 야채</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"II Mm @H UoRuvo (3 ZoVR 시우얘 U 새밥화 밑 우부 '시B반 제법 U5 까도하고 옛7니다 60 G?Bd C에) 문 제무은 관접 고시 년 몹시a 입까지바 VFORLO 연 (티길 0? 0-8363 굽시다 연양정보 uTa OMIV FN Nu 소고기 입유 bNI 원산지 Kurmi Comw harlbo; WWW 터키</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8 9 COUU 1apan미 퍼지문지리_; 소비기래 이신 '리사리지밥산-- 수입 판대인 스배: 질로-품물주 료록집주_로립하문@ 도S 백신당-플옥주수전다; 플도 텍스트렉 포도관 '전진자현문 쫓대 물관 개품 후가금적 시E님 '피해보장 피해 및 구입간 미어 미합 399 문저: 본 스신수 국번없이 무전 '깨끗히  'o시젠트 보미는 2 듯 모 푹 쇼 ("우 'Rer OaIOMFODD 메주- 주오리2 그리세린사렉신예 [감치하테이크기(김자, 요소제 신도소럽제2 ~리리 E요 구연산]. '민길자맛분만 '실제소금 습뇨가 시O성크림 '직사찮신, 있습니대 안심히고 신고 이므로 , 굉팅식문 반심은 ZII 초23 편집 TK Chocrip 기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00 8  3 '어쨌리? 눈말 40 셋 233 (행점 '의한 유 힘 8 '7후리로L보 6 명 758 % ASI23tzgyligrg oTDDSU2 (생포로사 올리기유 조릿공품 '유화지 5린 학심 [가공유제경의유) 비E오다 17399. 냄저 '소비지기밥벌다 요이다 [명양정보 62876 '지도함위 LmPI '직장선및 y시고L Ia 내L꾸다 {보움 [물E 내용량 Doo피 EmDal Ey배Og 349 190 kcal I5q 'B0SX [`기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OOI Muamd Tryuliiors 09 Dpnilina Iarti Uonna 교4 poslor Oumulise( 4m wo) Wheat Soteawoylom dimiT SmnAS MikzNnavulloy 600Fax 2I2 ";어 거없0 UI '리가 미어 '다I 3 '대터니다 영양징보 098 BIO 입 ou oity K9 AyD' (Naiai]) ODa +90 구UU M 0 1.Xw O/vu 'n기 Gom 'horlbo WWW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133353_jpg.rf.5e6f59227143fff9dbf806cfac7fad26_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133608_jpg.rf.ce798d41b7948148205776e62f76ac1d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-MILK|B-SOY|B-PEANUT|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-SOY|B-EGG|B-MILK|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제품명 : 권더 조골핏 쿠리이이이 식품유형 : 준조클렉 이야기락 총 우유성분 : 3396. 충 코코야인로 1393 원재료명 : 밀크조골렉 4096 (설탕 전지분유 우리마이 0 코코아버터 코코아매스 레시린 향료 이어기만 (바닐린향)) , 설탕, 탈지분유 식물성지방 무수유지방 레시린 향료바닐리향) Oe 알레로기 정보:우유 대무 합유 제조원 Ferrero FoodlHangzhou) Co Lid QR코드스랜무 어플레이두다운로드 수입원 : 폐레로 아시야 리미티드 한국지점 STORY 이일랜드록선댁 (반물교환업무 소재지: 경기도 평택시 진위면 진위서로 63) 판매원 : 매일유업주) 경기도 우리아이외 함께다양한이야기블 평택시 진위면 진위서로 63 직사장선들 단들고 위고 또든어보세요 피해 건조하고 서늘한 곳에 보관 톤 제품은 그라-기 로야 코다; 스" 컴우 2시간 공정거래위원회 고시에 의거 고환 또는 보상 미다-기 이미데당 모이서새국_이야기념 받울 수 있습니다 부정: 불량식품 신고는 수입주L다 5PPO 느 이33053 업애 미미미심 수 국번없이 1399 고객상담실 : 1588-1559 하다 반품 및 교환 : 구입처 및 수입원 영양정보 내용량 509 284kcal 나르문 615rig 39이 | 탑수화물 2720 8%| 당류 26.79 2796  지방 1759 328 트랜스지방 029 포화지방 1139 759 콤레스템물 175mg 66 단백질스49 896 갈술 I5Omig 21% 인 1225ma 18*6 1 영입성분 기준기언 대한 비어찌은2@아m 기준이므로 개인의 밀교 입림에 미라 힘글니다 8017"7609 원신지; 중국 소비기합(입원년 까지) 옆면 표기 상상이 재f는</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직품유히 건다하| 내용히 509 그리l어저 %교운ml 부부백; 콤어 위요-문-흥l l _인 안생로 7길 ? [흉목보고로200V @ 3 소비기한 {우면 표기일까지 잘리린 0 [로궁l륭 물히 올리고등-사고동- 353 #섯리먹탄? 2 오도-철제, 산도조절제2 산도중적제? [졸- 불전적일하지겹다 }문유지강3요 롭_ 심장속소 청제수 시자항색소. 대두 땅공 흔입가능 '직사콤_물 피양여 호도  은 '중안 대두 요공 동록 '급적 불러듯집시용 그관 및 반문 본시고_상담실 및 신고논 야므l 신공호다 '번없이 1399 과랑 접심지 4 내설신 60 9 160 Kcal 15 05 25 소비동 영a밥 온입재제 프리 돼지고기.위 중말 유증송이  소비사 영업스  @ 이래 : 58 75 닐9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제품명 고구마형과자 내용량 162 @ 식품유형| 과자(유탕처리제품) (업소명 (주) 코스모스제과 / 경기다꿀 '소저제주사 진접습 플강픽 kI http:llwww csms co (스비기한|후면표기일까지 판 "to SII [민구#말늄지국 d-토코페 '엿 딱 새 98 % , (원재료명 1 청제소 크림해 알 남압 960번길 '캐나다) '창[팔록렉인유 (발렉8,1o ; l(혼합히] 탓 콩대문(한로_ Uo; 물 글리 '씨해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|오징어|대두|우유|새우|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 달걀, 우유, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134026_jpg.rf.4c1217df5150fb504b6a4da92d90376d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134041_jpg.rf.03b9cf371e46c2eacede4e7f81371000_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134117_jpg.rf.f9193e833be81b64775c29fcaa2cfd03_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134119_jpg.rf.eade0face448cf26d1fa1ad54343f344_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134152_jpg.rf.34350a82e718c40cde60fd81b9f12141_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134144_jpg.rf.3d2eac697070e6189daeeaeb7208d789_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134218_jpg.rf.a4d1c3d0478a16e00791234c97797429_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영양정_ (생 ]양m권 오리지 식로"리가재유탕_리제 내용3당 소매분말 미국산) 옥수수전워옥수 괴국센다 가리 L S30mI (서르베야 등} 햄위말레이시이산) 번핸물 기능대유 양 589 맛메이스콤실탕 분말실물로 "'질조금 회기내출 액 탄수교물 대료명 (주 -말방렉속 상기포로스 가e럽 -내@스트 당류 59 (쉽jn하a %u동물액중국신 gi 이넷 다 휴@ 식이남요 " 최 대도요요 각지D -로비t확길학발유 지방 169 포장재질|프리프로하 트랜스지랑 스-[후면 끄기언까지 ~30 포화지방이 푹보고반? D-품-끔- @aim@@l금 그스템 또토늦 거 새우 계란 땅콩 맑고 오8어 단격집 239 ^동안 저품과 같은 시-어서 제소하고 아습내다하 가익 하어1다 [책장선올 피하고 시불히고 건소한 곳에 가념 무 바로 느심시오 "국덮어문 검은 청은 원료 중일부분으로 ! 드잡시오 '소비지기본번에 이기 교한 '1499 ";민없이 '불식늄 '"꿈년사및 신센5 유사a DWN 조개료신복 보진하십시오 Veoras '인심하다 '무해하오니 인제에 a 드망다 '인분해 rMO OVis A 신고논 '아보 U 구입한 농실 신소습신포심님 위대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ocr_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>image_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>readable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|밀|대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|돼지고기|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돼지고기|복숭아|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>unreadable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 돼지고기 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|우유|대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 우유, 대두, 아황산류 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 대두, 계란, 우유 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 우유, 대두, 땅콩 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소고기, 토마토, 복숭아 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>#</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134452_jpg.rf.07dee26761afdb0e017c1b4270c29e60_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134424_jpg.rf.5a5c3c7ee9ab5850c8302f6fcb84ca18_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134440_jpg.rf.bd9b05ec7ce0d5619a3444b493ba2df1_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134428_jpg.rf.2049c5d825fcaa6fc9e1b2faff46e48d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134419_jpg.rf.c7b189faeee04139c48c432ce16ebdc0_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134434_jpg.rf.3ea558dceef5998006bba37b9839410f_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134457_jpg.rf.e6b8508e9e5ce7a90ea9d49c2efc7473_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133643_jpg.rf.6c69f3e3051a0711e1d9fcd9ae05ec32_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134258_jpg.rf.b5b5e0a48f4851716aefd7995d3e7d70_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133646_jpg.rf.d1d156215bc8d75c50e0fed0cff8aa62_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133722_jpg.rf.36af60d9cafeb74cd30a3850599b1e0f_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133634_jpg.rf.753889fd0fce8764aa39121ac9f18adb_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134056_jpg.rf.7dbf04349226ca02326439c8cb63cfd8_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134912_jpg.rf.fa9ad12d1b6eec77586399144cf94d52_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133344_jpg.rf.e48cc88355eed51e52467cc0af78e13b_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134750_jpg.rf.e796a2b61a281428b46f40cd451e9482_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133627_jpg.rf.9229bc83ef7c2ce234bb6c908a7bb049_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133326_jpg.rf.4f05b90e1231f0a37a569ad728219b9b_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_135034_jpg.rf.fce49c5fd42aff4cf8d899b8ab9138c2_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133355_jpg.rf.932836217ffce9ecc65bb050612f908f_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133650_jpg.rf.42e201bf877c5ec52e99d6d2f3c8e863_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133831_jpg.rf.3327be8e6ebb2ddcae58f556d7acce68_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133848_jpg.rf.604060740d2b62c4a27514dd5db2ea45_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134101_jpg.rf.31291d284c56619b567920454c551aef_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_133930_jpg.rf.936283b369c239e4469cfafd88abcacd_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133638_jpg.rf.96aeb186d920b46a12a704fece16edd0_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_134044_jpg.rf.3f10895ccad6ea809c916ccbf47d337d_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133826_jpg.rf.1f05c7afad87c834729c4e69cf60ba12_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133836_jpg.rf.a82fbd4a8e62434e4006243ba19956e3_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133621_jpg.rf.c3887d6390bc4eff5679dbf75a4cc8d5_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133330_jpg.rf.de69efcddb15777fe221234b7399ec90_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133820_jpg.rf.f79bf52bfa23b06661c8bcd71e3817e9_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133656_jpg.rf.00a7cd51b1bc8474210a809df52eaac7_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test_20260614_133936_jpg.rf.e976887593a5dfdee0dfd24c75ea13b1_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_133327_jpg.rf.6ad8b7bc052fe267dc6cb186f362f394_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마켓오만니보기' urt87737하- #En# 건요법다 I 갖구위번듯 크러스트가살아있는 '이미지예 카페스타일 브라우니 더진해지고꾸덕해진 AIl New Browniel 브리우다 직품유리 조골릿가공품 소비기합 밑민 포기인까지 제물명 _미즈오 모장재질 문리프로밀런 [슬륭로하칙 @_자-임_지 서로오" 업소명 및 소새지 출요컵움 매음정퍼제V렉어지어퍼m전어유포물_신 l어다 l근; 푸어로히캐정말하국-음글량력 @ 야재물 진지로주포랑스신-멘표히로 코문아버터], 밀가루밀 미국신) 가공버터 '고보야분말 당류가공품 분 전텔액 갈색설다 기타설탕 매실탕 옥수수선분 백설탕 {가당연유 리업초고집 유크림 주정0 60 %| 내용량 240 gX I2개) 식염' 밀크로문크럼 , 요함제제탄산수소나트 [영양정보 1깨2 9 당 8 kaal 둘 산성피로인신나트급 , 쌀가루; 무마르산) , [일 영양성분 1009 담 (잔단경; 부수버터오일 항료 2종 [개 당 기준치예 대한비 6간 우유 대누 한문 40 mIg 2 % ig0 mg 10 % 호두 복숨이, 도마투 , 돼지고기 심 나트답 12 9 4 % 61 19 % '문류; 오4어 새우 개 ; 소개뒤(군 난수화념 8 % 41요4 술갑 모집) 손입가능 당류 8 9 39 제물의 친선 - 보론: 위대 진소로진 하멋 지밤 41 9 8 9 2 9 습니다 반문서 본사 및 구입럽 모랜스지밥 0.5 0 미만 05 9 미만 식사감선 ; 피해 온 넷' 국에 포회시밥 Y인 14 % I1g 79 * 모델 개본 부 기국석 빨리 드세:, 스Ha 1 "보 5 6 79 T 26 % 소비자 기난번에 의진 피해보심 2 9 6n고희 부심 김식움 신기 '밑없이 I301 Iu 소개센터 (선다) (MI 03-57U 떠마 : 기준지세 대다 Bcil 다) 무개 1572-Ay I냐dt: 개방 교 주3에 I 66 64 N J ' # 쇼 Ilf 'gD 닮고기; 주5기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서e Oi 휴e '마 나트 탄주 왕 V6 Oiiil 망따권다 오a사&lt; 하: '배y 트 (실문요형 어물 신문욕 마시요m시리제포) '밀휘이시야산). '외국산(러시아, 변성선분 정제소금 형가리 '가플리유 가4 화이내조 킬미w하a다시즈님 산) 양파 흔갑세세(댁 양파 트린 감사분말 oAWo 라; 식인 %:" 제방 9e Vo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 " 땅 0 만:이 2업 '임8률 we 그소사 Vo CO ' dos 버터팅 버터랑 IIO J소0 벼-'키 땅콩 드 (639 땅콩 고소간 GU 버터g3드 30 '땅콩심 5O '2말 지단과자 7다 매타지자 마자 메타자자 용 퍽 '0VO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전 조골렉과 바싹한 스틱 pOCNY 벌려스가 중은 초코스틱 [제물명 [포키 극세식품유형 본홀릿기콤품 내용량4 9 [원재료명 및 합량 |밀가루{밀호주산 50 % 미국산 25 %)} 설 [당 코코아매스(데덜란드산) 가공유지싱가포르산) 전지분유 소트님 코코아버터 정제소금 유화제t 향료5종 버터 산도조절 (제t 유화제2 흔합제제치자황색소 정제수 프로필런글리출 홍 [국색스) 산도조절제2 효모 흉소제 우유 대두 아황산류 함유 (소비기한 | 밑면 표기일까지 [품목보고번호[19940449005191 [포장재질| 플리프로필렉내포장면) [제 조원 |해태제과식품(입 / 첫안?공장 중남 천안시 서불구 성거움 진호8길 67-26 [유통전문 |글리코해태(주) / [판 매 원 서울특별시 용산고 한강대로 7긴 3(남영동) "직사광선 및 습기찬 곳흡 피하여 서늘하고 동둥이 살되든 국에 보관하여 주십시오 본 세품은 광성기래위원회 고시에 의거 피해보상 고개만속실: 수신사 요몸부다 (080-333 16677) 부정 십림식섭 신고논 국민없이 ! ANI 반문 및 n다 청소: 본시 및 주Pa *이 세,은 '바노터 사농i 세a 마 간은 세소시신에시 새소히 4 깊심니다 *;둠중 온도 네 (뇌에 미 하인 반신 나논 하진 4{io이 새리 수 있우나 인 제에 무해하다 '서 "카니다 2 ( 이하 보관하시면 맛외 Ix kY 예기신 싶e니다 대안w : 내에 시 민 판매 ) 허용민 세습씹니다 WWIM CuAI OLuZtCal TO WW 8 7민주요 F8나 아제리; 150 5 *</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1405 ' 조관접 74 Tnr OoN rkso 'oNuE 스타일 쓰라우니 (W 카때 V Mared D스: 17 화선님 ~건문' CBBn9 초 (5 %트 Keto ^및 고심 대한 78 2다 '리엌 럼 톤 )re 초코 년 2좀 대뉴 환문 429 8다 3 쇠 89 83 밑 당류 419 , 미만 P5 최시 개; 지방 059 {4다 rg @ 새우 . 219 7 ;두 55 심 곳 {6m3 2e 딴 및 낯은 {9 채 반물자 온 불망 다 인 e 의한 국단하이 개봄 보관 0- 0y 둘 무성 고객' 로자 터 MYw '"a 신배시고 로u 건기심 레브닐스 = 씌다성유제민터이시야신) 호수산베터지다 오리? 대P 그조이 '가공버티 940 '재지] 잔셋정매당 , '미산) 민가주 (민 유어 기타선량 배션 (영양정보 N3# 국고하버터] 주0 영망생군 '재 "합제제단산수 소나트 간새신딩 유구램, 신린액 똑아로산) ' '기준치다 어개 텅 Fye '살가루 기당언규 쇼9 (나트움 '인산다다 민1 창료 29 [단수화다 우유 식망 신성미로드 부수버터오이 05 9 미솔 달간 '돼지고기; 조개류국 토마도 신단경 복숨아 트랜스지방 하면 ` 리 오징어, '집소중전 69 포화지방 '당고기 기준지석대반 비S온UTA 손입기능 위해 구입한 P수W나다) 보존움 곳에 (플러스비: '대수 모함) 본사 신선도 (@캠^미피라드 습도가' 단렉진 드세요 꿈의 {영양성분 - ~가인의 '피해 불리 '피해보상 1339 '가급적` 기준미모로 '식사장선: 570 '기본번에 = 신고 '량식품 비자 (전화) II 센터 152 ?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|쇠고기|대두|우유|돼지고기|조개류(바지락, 굴)|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|O|B-SOY|B-MILK|O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-EGG|B-MILK|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥순수 뵙이 '202600231m 제품명 옥수주트이론 제품:! 특 의문유회 [스주껍"_발[ 교질 의 겁질다 눈음 업소명 및 실현대로 @이버길 30 속부문만율 진로주 소자지 컴프기인까진 입맛의 감혹바 소비기한 교oag@ 때 한걸 더 헌 불불델면렉 국산 호주 부 쾌가 가표 (리국룻되-꿈록g이%3 자손만대 옷 제탑10% '문a유외숙- 태 현료명 중리4% 국산 만레이 국4드 '생리렉트 양정보 대무 입유 호갑답 킬로 J75.6m요 힘습니다 71 밑 뒷티이 = 도에 '히집o 10.02 제 어논 Q 소비자 스시 we 이 미사 건조 오 혹수수가루(외 {%,깜유외 시O)1.59 , #리프로"로PP) [200406073143 49 가동설인 . 큰입 회으다 따력 저U서 마지)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>" O 9 DRIS 서AIT Sable 사브레 oKIGINATEI FR&gt;M YKANCW "I &amp; uA'5Cal UEII 1076 버디 해) 사브레 ' ' '; SS '849 1,600 ' ' MUIIMVW ' I O TCDT 리자 무N 예Y A 도장재심 "리다 _리내터 리 내행 %0 BaAD'OUS22I 영업소의 명칭 및 소재지 기0가;: 메미국신) 삼답 소다 {납유주#되레이시야신) (미래미시야 렌시터 집시' 뉴님 마; 리아세다 @입하다] 리서긴지밥산예스데 대누무 리아세다루 '비 I민I? 성합다 "개대 그시어 3내하다 * 들기' U어 '반합' 교실심 [전 떠고가3불l적 DIII 사과 국어없이 1399 eloen 데주시 버시 깜ut고 VwFtuk 93 9 399 ! 급굳이 스애 3그다지르 '일어신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대두|우유|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대두, 우유 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|대두|우유|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C 드 43 소 - 낱g 구 로로) Tgmmtran 유수 문 상' 식n유영 마작 중말 D8 0A위 암기유 '3유 오징어 P: 원재로명 '리서관; 포도텅 주머리 여 유장 50599 '터시린 (텅로 주인 25 0 패x - 보 시드하다 beeri 0X23제 정요지 가공요요스요389 분히스 06433오3신로조 99 호주진 어스러로회위금스터야린유하ID 인기루만 미 야사요 은현보다 '8제서 {하오현v리 식_성유제럽워다하이시나신 스웨이린요라리이시야진) USa드 MI 흐려오러진서이제 코모고어금미만3이)이신 '합리시청러인신어스t. 성물소 88? 올리오리진서이째 렉사 수수진 [g로고르3 비 '가려시' 외FU 표기인까제미입인 ': 신문 L무소묘보g다 강인도 소비기한 | 유인회사/ 인신표_O 미기망 바 [용시시'주 제즈원 유용신문만대권 O83 '9uo u 딸바</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50 5 제1 (국색스 Ne 밀 우유 대륙 [소비기화 |말런 또기히하집물표보고a IIYAMOe 포장재질|몰리프로필로내포장면 해태제과식품(주) / 천안2공장 (제 조원 |중법 천요스 지률- |울 n@호 [유통전문 올림언해대짚구 [길 기히하다 '용신구 컬리다 [판 매 원 및 '본 미벼 '38* #8 곳 *이 '생격 주 내내' '하안 7 k 소골되다 벌스가' 사사) 주 스틱 NKy {관틱 [제품명 [포키 극세식품유다 조골렉가공품 [원재료명 및 '당 코코아매스데덜관드산) 가공유제성가교로산 합량 | [밀가루밀호주산 소트님 떠gP 코코아버터; W? '미국신 Sv '정제소금. 유화제2 흔합제제치자황색소 유화제] '항금 8대터 산도조절제2 효모 호소제 정제수 프로미 하&amp; 이황산류 한강대로 서울특별시 충륭이 서늘히고 피하여 습기찬 곳을 '공성거대워원화 세물은 직사광선 ((KU ` '요금부럼 ( 주십시오 '수신자 보관하여 W '고객만족실: '국번없이 곳에 N3r 도미도] 피해보상 신고는 '세중온 '불랑식품 = (의거 힘으나 '있습니다 ` '부정' 구입한 '세조하고 보다하스 6677) ' #년송이 . 'U이하로 보사 및 I석예서 불하이터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 대두, 토마토, 쇠고기, 닭고기, 새우 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예이스 유리 2150 해)에이스 _ 5S00 ; JU4 980 V JI 캐 이) od PDe) (엉남정보 O : 09 [죄당 지O텅 진드에미스 무요로 소비기다 문요표기인짐 )다 '지O 기 쥐 _유어 고재롭증터제 포장지진 도금품동재품렉-하린어스트 요;로사하 허복금기언- 미해보 실물표호 '9920u8i03 % [발퓨 @하- 후흰미뜻--_물히다요요 재료- @a@놓 고기만 수선장_ 권기 명 '유회제 레시린 d 기타_템입전||듯러0h 주9 지 밝히 불l늄하p이j -기물 -자련_탕다름a다 붐O-#피로 신고트 [물_- 제인움 O-가하큼 유국유자강궁-시가_미기리 기표내u 한입업 :이_a85 모현지 [불 지동움 정제}자현서문위공워국미-_갈주이[체유국즈lay 요{유하 -로" [토론가공내다 8저속로현세오--기 -콤품유 이제 스끗 지불교공 T7 [신도조건재 . 호소제 말 구해R도 진회.진구 꽂과정로 2외되로: 자언 '무르게 년; 꽤 i0다오 제 스동- _ u l_조요자지도 1모0 MhCoWI 따리 제조 원 W 주무 대 꽂-치훨전모 희카대로 그즈럽연터 판교피서다 시 #뜻 ele 3 &gt; 5 샌드 P비야 W비O 시하고다 피하어 '관히다 ek 회로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쇼 집 팀 액 '힘) '밑 석 7 '수면 대륙 요요물우 원 머무보' 마도 산 게 와 I사분 관단 재표명 [오징어집 {버구이맛 (맥분(말_ [옥수수: '미국산) 식문요영 (인재료명 '외국산리시야 [오징어유오징어 외국산 깜유말레이시야산) [재요당_리 [인산니트트 형가리 (오징어맛조미분말 세르비아등 '버터구이오징어맛시증 옥수스 소비물드 [자주색고 (이맛 플리인신나트 '구마색소 소비기인 오징어맛조미분말- 오징어 [파보 카카오색소 오징어주리스 고멘호 #기일까지 @대시고기 텍스트린 [19910461101 ` 입유 g리l o이 되고기 'j성하 (생선y 4리) Io720I54001 E 물리n로 '미이자 '사궁히 신? '쇠고기 새금과 시멘이i 신수득 1"세세 #대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[려; 해매버 미 @i하| 7 인 '#로 [제기해 호; [쓸픽워 떼비 l월드 탕 [ a %공유34 #너 I야 7J x [지 p대 |쨌질드 (국산; 다두 (무 입구 #시히 ma이 UII M 믿히다` 인대잡 O6e 1 MJ" j0 ^ ; (오오k | '무렵 소등 (소지 '#Qa오' '4외'} 디의기 {후어표]버T지 '식물성유지금올렉민우 '뒤경씌 스고스 "외국쇄- 퀴 {토도뉴도도_ '마음노신:; 중국산; '최국산인도산 '497터- '사괴능주자중다 '드t2보]대k 발요식최[ 1귀신; 겨고기 = '인도니시미사 ' [브매치간핏 ' 7937 onioN {#음넷 국씬 '쇠고}_ {도미보 I0 F4: 47 오119091 300 Naa너 실 미다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>흉내내 PIO G너| 나 비스금 일 유당 설탕 [공버터 당류가공품 전분) '전관색 [방세럽불d하밥-방@ 감신도생@다 무 [리세린지방_에스로 햄수 바무 주정프로런_다 신3 ' ' 35n8 LC 제조원 어물시엉동꾸구트 제지미취 과회산업3로 '양로 중청묵도 소비기한 청수사정원구 '188 [면꾸기일까지언 요음 품목보고번호 120010415034793 원재로명 [식물성크램- (혼합분위 기공유지상기하로미) '말치혼합분말] 등 (테르회유금유; '밀가루말E 믿입분웨외국) '미국신) '말레이시야산)) 소트비가공유제업시 [야린유] 기타설탕(원당 _ '판위말리이시이신) 우지가공우새장스 '코코이분말 _ (본일분유-유하다 눈일가 변성전분; 정제소금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크 버터오 2,600 [내티q뜰 내용량 1g 소비기한 믿면 표기일깨지 몇 { 지 (대전광역시 s팀 6번길 57 'GA AePP 국산 밥유 = 푹 곁 II '@텅 Ii0og 4y '비표 타수 'M '허리 '대 / It} 17 법유 7 0 % 시밥 썩 P 1 Y 3 F '시법 엔 '세 1 9 80 % 9 92 % 19 % U mllle 수발움 물리프로필렌 WWA다: 업소명 (크라운제과 / [ 머녀구 = 신실서로 소진구신 '가공버테내덜관드산: 샌소히 {드립구진 '유지방 (전관세 "신드조청제2중 , 유화제2 출함분유; {'과재가공품 , 올레오레지로 엉양정보 (N64 '45/ 'kCal '나뭇다 8장하신 I순 또화시미 W' 'WX Ko 와U'1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1E 버터와뜰 '버터와뜰 내 용 량 135 9 소비기만 세품 명 플리프로결렌 식품 유힘 과자 포장재질 프프러올-과 다다 품목 200802423765 월소망지 주덕주 07 보고번호 및 보지명 물기로_말-미국스닭 그율버뒷번물관- 완하다_ 줄자m그름렉_ 소현실 저 해국산 홍중 흙 정제소금 생국럽레신; 조메리 함료 밑 대두 계란 우유 함유 'O콩 다-그기 쇠고기 흑입 영양정보 가능 교환 켓 반품 본사 고객 상점실 및 영업소 혹문 구입한 100 9담 곳 직사랑신올 피하고 온도' 습도가 낮으염 둥둥이 잘 되는 나트움 340 img 곳에 보관해 주십시오; 단수화물 74 9 부정 ' 물탕식움 신고는 국번 담류 y 9 '없01399 소비자 기본번에 지밥 16 9 의란 '피해보상 09 '(서울) 977-2580 (주신치요금부7)080-709-2580 또화지밥 I' 9 레스데 95 IIW 단백질 맘 학 Pa muller 신일서로 트랜스시방 | '고객상담실: ( Uel V사 시대 어반히벼 O터리 "7oiil 73709</x:t>
-  </x:si>
-  <x:si>
-    <x:t>어; 아이비 ('쿠 d 25 % *% 50 및 식a 텅 6I 유유 C 구 조원 단 I 돈 및 9 럭 C 9 여 8 pOCKy 스틱 [대용광M '바싹반 초코스틱 ,미국산 신시 [조'릿가공품 '4뇨 #콜리과 _ 버터신도? 코코아매스데표관드산) 가공유재싱가포르산 , (리 . [밀가루만호주산 탤써스가 [포기극세식품유형 1,항료5송, '피컨. 프로 유화제]; JigyMAYYNI '정제수 , {합량| '코코아버터 정제소금; [제품영 흔합제제치자방색소 [원재료명 소제 꿈목보고번회 요모 이어신류 입원 '전제2 소트님 [제 유화제2 사드조 '천인2공장 전391 (대모상면 이까지 구색소) 기념'다 '성거다 해탤제과식3(주) / '씹이 a로 7? 가다 '한강대로 스비기 '고 '꺼0시 포장재 집성거; VY) 국리코하대주) '피하여 Gaug 겨쩐은 N8 보명시 2543 {유용전원) 스신 숨기신 구멍선이 주심시오 고인순 생 신고다 y성 오르하여 '굉장식협 그적오상 모다 구입원 우 [회거 ) 모새 F:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유, 땅콩, 계란, 밀, 쇠고기, 대두 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89 우 제 P다 8 700 엉양정보 싸신' 80"9 내#yi 489 단수화다 09 09 당류 209 렌스지빵 99 Oa 지망 포라지생 스U3 '8020 대부무)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥스다 K 09 이 mI [H 소 O 이 (O 6 거개 기) 25까지 2026, N리INa WN '제Iila GM 입소입 기인N 소새N Ved OOaliBokCa '(0EN 'io 109 없새요버 06 'Noll</x:t>
-  </x:si>
-  <x:si>
-    <x:t>'이미s {Ni워 애5M 95장a*기 0' 국결내} { {* Y청w]l8' 79 2봄입 1": 383": 0N3 939 1,400 CROMN ' OAN 9 거 WSII 은 그번 #기뻐스 임망 내 음 김 99 고소기 밀콤샌드 포장내신 {엘리"로 민레 5 [업소명 맛 소o지 (취하세기 Cri이시OC사]고은 심금; 하현이 시야상 -불# 단수} W? ~NnAZTGI% 인-만없이지야템_ 별_ 입뇨주 -"#이시야진@ 중E 권 불히다 업월물 텅 ml '밀기 퀴미 미국산) m트템뤄다 '점금문문 사 n습 품국산} 덜시 로대산j유회제협 #다: 비타민도 대잡리 '지밥 정화대#적다 만_이시야켓@다다] 햇당버다 설뒷 밝화 '청제소금루 _물장문백 국내산) E' 신도조신제3#; 메중국신) 밥유 '및 굉섭스 ;온 구입히 고 #드되품유-유-- 임기; 고 입 고 방째 '주십시다 개권 피하고 관도 ;수가 '어다 많이 미신 씨내심 '식사관선3 국민언이 137 예사 기쁨 무심 시다신기 "심사요급부탕M0-10}-%M "과대심터다; (Aaln eM0수 yWa 땅콩새드 고소한 ( {입82712X {aljyllzl ' c하스 이스 c어스 회번 신외서로 ,전정버 12 '빵하버터 , 고개심다씨 K ''에</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부: 통크 우유 제 품 명통크 초코 식문유형 | 과재유처리제품) 소비기한 | 믿면표기일까지 [포장재질 | 꾸리프로필럽 업소명 뜻 | 주요리올제-의사루장 전묵특별자치도 '소재지 [일핏콤록실렉철등 식물성유지] 말려미지i 52 l름롭플플핸플출__-요 집물영로자 쫓하 하 전지문유 뉴질런도_ 미국산) , 백설탕 RII '미숙자가나다-;_ 밀 우유 대투 참유 호두 동: 교해해출? 날은 달걀; 새우_게; (전화 83 오 예입할 피적 '부정 : 불람 @론0 개통후 곳 20 '본사 및 16 &gt; 1y 74 3 % 0a 55 mE 22 % % 시방 1285 8lo '본언 그따런 이미스크림?' 식물성유지 전립분(말 산도조절제 알파밀가루; 19830487051139 되고기 '최고기 돼지고기 , 품목보고번호[ 소비사 토마토 워입가능 복숨이 "슬도가 땅콩; '조개류(굴 '0* 027 '피해 '직사광선올 국건#이 '고객센터 . 징어, 피해보상 '식훨신고 빨리 드세요 1522-4002 . 가a 구입한 (문자) 48 5700 내용림_ 반물처 [팅# 16 # 399 '흐 9 '모라지) {민주의 영양정보 트랜스시방 스스 {단백심 나른움 UA미만 V84 0무 플레스데로 'I6 UN 예미히 Veo300 il</x:t>
-  </x:si>
-  <x:si>
-    <x:t>088 28 403 다리04/ 어가, 미니사이주/ 파디 '나툼포3되어 보관 쿠대가 감리/ 리온 T '7 고장재집 "리프로미; 미국신 외 기물보다 식물-무---슬가 불g 회지출텔 . -컴무지심유 (샌후장유생동되이시야심) 전지 _신염 '땀플레인유 우유 대두 소바다 ?액적 손리 의한 0' '부정 개 ; 중 4002 신고 피해 a 습로 10 ; '80 8140 반물치: 및 1399 오 17 / 곳 1 8 특-치방 8 % 8당 10 % FB 63 40 '떠리다 9 8 제 살 3 " 어내 No4 가` Pnet 5 알레이시야산; '편지늄유; 오드구런지 신도조핑데 6 DI_사과 물목보고런오 719760487005157 함유 도마도 , '돼지고기 &amp;^ 직고가 기본범에 닮고기 오징어 '피해보상` 재우 050 드N요 직사장선올 영양성보 '조개류 ST0 풍 (문자)1522- 중앙식꿀 ' 내용량 굳 '국번없이 m 본사 '8X 2봉지) 국주스옛{ [보소화물 구입한 @5 1봉지(40 308미관 20B VGAFV 실 ']3WT버터fW? 197 당류 '단백짐 O8 kcal IO8 포화지방 (주오리온 38 58 O디e 라니의 S HCO '입하다다 801117" '280512</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5 cp 신 '셋 생 * 수 이o 셈 ? 9 '%% 시o @ 4 시 739 y 2 J 5 7 혀 '양 { 터 명 ( 록 북 1 법 6 평 C9 털 약 1 품 { 뻔 말 [ 몇 @일 1 (o ' % 7 @ % 롬 훨제3든 턱 8 #</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카누 83 4 4 4 Io 437 l유 450 라떼 W oS자다{ 오aL 6C 에 너지 액티드 BCNA 에너지바 어시) mI DA 65 03 'mmo Q 백런스 CIEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영임정보 Vagonoirt 꼬진 WJly YU- 225 ! ! 1 E 2! 6 914973"503139 보미하다5 고모끼: NBFoauy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>너시 먹들 로리시닐) (식품유-곡류가공품 [내용량 | 70 9 [현재료명옥수수 659 (미국산) 소트 [마가공유지(팔올레인예스테름화유(말래 (이시야산) 깜스데하라예스데로화유 애 자메스레측화유} 대륙유외국산 아르회 티나 미국 브라질 등) 가공유제광경 (회유; 항료} 기렇조V미국분정생소움 비타민82 항금 , 항문기] 대는 후유합위 소비기해 전면 하단 표기일까지 불고방베식사공품물 피하고용-숙소개 l안어 봉문이활 도는 |예 실온봇관 업소명 a [대_패렇물킬로로 17 영천시 소재지 [포장재적탤쪽 푹 '핑수 [품목보고번호7988055500812 알류 땅정 고등어 게 [r짚-- 료중하오0 화훈물 '때 지 합 포함) 조부외설다 분행 해물 의기 교환 는 "분움 심부퍼서 '힘습니다 박택망 및 "문개심다삶 그표 집고다' '객상님 '080-900-61331주 '푹부보? 고y 부덤 d Sajo cok '깨끗한 매모이 무리미금 깨애 기이기 부성 설리 시합 신고논;대 없이 1 3*9) VI 제주 [영양정보 UV터 7 9 345 기둥시어 대인 (UO W") 30 % 13 % 1파라 (회산면 혜목% 태위원회 우리치연 주의 서회 kcal 내표빌딩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C 드 l 4 770 애 식집유임 괴자 운림 IDaEDDKCaIED gX23지I) 몹시모장재집 [ 리프로 반품 및 교집장소 민기루민 미국산 소주신) 신망 옥수수진문_ 시르성유제기공유지다 멋r중말진하출 수@필유 불불양하이늄 아지유) 기공유지리어스데`화위다 '보관산 주의사장 스테야라위만리이시야신) 야지유} '해바라기유"손신-계-레오레진로조D력 이I입리E7 웬재규명 물렉용렉질십어지] 죄인전유스륙 워리이시이다 셋약-간_-일계지혜바라지 새우 되지고기 리세린국 라리시손레인신예스리트 성제수 손.제제q레오래진로 오징어 주머리 그리오래진세이지] 모도망 코로이분매먼다이시야신 53 네 트a 시청이서 표로 잎 469) 5.93 옆 옥수수진문 화물- 명장제; 평가제? 정제4 유r 인로제세 소비지기본 (보로 캐러인시템 레시린 Y 대투 구구) 보심해 소비기하 [ 9민 표기인까재비회인) 무보고런금 {9n60397D65-207 불]뀌다 우야 깨소인 미기밥 유:회사 / 강신도 원문 김외9 외리돌 그망이? 신고 유' 전문판매 길 5시시-주) / 인신밥의시 무B구 도마 U25 그 @ S 기 아 030o 93yo Auu E바</x:t>
-  </x:si>
-  <x:si>
-    <x:t>근 6OO 크라운 4 7003 2 60T [버터와돌 꼭자 내용량 135 5 고대' U로 신립 신입; 대전 계만 산도터 Iu '무유 활유 23 , 년사 입 2 I00 9탑 "대 탑 시% WN billtr 내 (n다 ''머티라&amp; ': ?A ` #두새: 밑연모Ty리 시멩기 'NFXYUA,5 소비기안 둘리프로필렌 '7PS' 엎소대 5 '히;;; 'x제지 자그라운제과 / 요거R '미국산) '대디구 '거 스머리 'L어입남심 '경제 가장버터 서로 밀다도 67번 '전화국산) (네덜관드산: 조리재 ' '모기고기 과재가공꿈 '식고기 '합분 드 고 영양정보 구입다 '미a '나뭇 O '민수하다 {에 rnu )yII 퇴w 6] 시 '화기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134011_jpg.rf.08bdb8c3164bc63c496449d14dbe9864_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134018_jpg.rf.abfe047d302ad80dfcec54e925050521_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134252_jpg.rf.1a10ecca006dc5c4c20bd5c29f217bd9_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134250_jpg.rf.cf2481ea6f846741c7157ca4dc4d12c4_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_20260614_134332_jpg.rf.57398403f0532065a14f118a7bae2e33_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>valid_20260614_134336_jpg.rf.ab4506c3110a6df4bac04f4465f4839e_0.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3w28 3심 8 2 S 9, 78 9 임이 06 Y 의+9 &gt; NS' '6s 83 8 8 1 6 5 ' # e (A ; 무_ 근 I 해 " ' 1 ' 틈 5E30 3 틈 '뜻어[하나 틈 " 점 코코이튼 분 @ Jun8 {물정유재 N 면 (트려어사 방 J로 콩 3634 '4i, 8 '#;력 Nm ariasan</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 달걀, 우유, 대두, 토마토, 쇠고기, 오징어, 조개류(굴) 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-MILK|B-PEANUT|B-EGG|B-WHEAT|O|B-SOY|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 쇠고기, 대두, 우유, 돼지고기, 조개류(바지락, 굴) 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-EGG|B-MILK|B-SOY|O|O|O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0 (%)) K 먹먹는 분연의 동크 그미로 우유 ( 스 제 풀 명동크 초코 식품유형 | 과지(유처리제품) 소비기한 | 믿면포기일까지 포장재질 | 플리프로필렌 업소명및 | 취오리혼 제3의산공장 전묵특별차치도 소재지 의산시 통서로 377 원재로명 _통크 조골릿(백설탕 식물성유지다 말레이시야산 전지분유 뉴질랜드산 식물성유지2 코코아매스), 밀가루(말 미국산, 캐나다산) , 전립분(밀 미국산) , 식물성유지, 백설탕; 알파밀가루, 식염, 산도조절제 우유 대문 합유 품목보고번호] 19830487051139 달간, 땅콩, 호투_복숨이 토마토; 돼지고기 신고기 타고기 오징어 대후' 게 '소개류(물 콩합 모함) 종입가늘 소비자 기 본-에 의한 피해로상 "취진공선흘 미해 콩 숨문가 낮은 떼예 도분 개T루 가급적 빨리 드새요 고객센터 (전화) 080-03 5700 (문자) 1522-4002 부성 '불랍 식물신고 : 국면없이 399 반갑처 본사 및 구입한 곳 내용고 458 23619al 영양정보 3 %0 [민수화물 28 해당; 16 3 16 나뭇 '' I터 사화시밥 1 8 47 지빛 12 팀 22 % 스시방 0 터 7 컴레스 %라배 4 고 끼운미내 WI NCCI T20su0 방법 {이미스크림 8 9 '미민</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설탕, 포도당시럽, 팜유, 구연산, 덱스트린, 변성전분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀, 오징어, 대두, 우유, 새우 함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우유|땅콩|계란|밀|쇠고기|대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|대두|토마토|쇠고기|닭고기|새우|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B-WHEAT|B-SOY|O|O|O|O|O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S 유통전문미 ) 못데웬포드취 서물시 영등포구 양평로21길25 제조원 국제제과쥐 중청묵도 청추시 청원구 오청흡 과학신업3로i88 제비기한 [연요기일까지연월일) 직품유형 [과자 품목물고번호 120010415034793 [포장재집플리프로필렌 원재로명 (식물성크램[가공유지싱가포르산) 설탕 흔함분위외국산) 8 80 (혼입분위 유당 말치흔합분말] 밀가루(말; 미국산) 소트님가공유지 관에스 l테로화유되유 말레이시야산)) 판유(말레이시야산) 우지 가공유재 팔스테 [야린유] 기타설탕(원당 전분) 코코야분말 전관액 흔함분유유청단백분말가 (공버터 당류기공품 변성전분 정제소금 산도조절제2종 커피농축액 글리세린 [지방신에스테로 손합제제합성항료 천연함료 주점 프로필런글리i 젖산 글 (리세린지방신에스데로 정제수) 바닐린 무유대- 고기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|계란|우유|대두|함유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀|쇠고기|우유|대두|함유</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -888,8 +1035,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1553,1824 +1700,2126 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
       <x:c r="A2" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>134</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
       <x:c r="A8" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
       <x:c r="A9" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
       <x:c r="A10" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
       <x:c r="A14" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
       <x:c r="A17" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
       <x:c r="A19" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
       <x:c r="A22" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
       <x:c r="A24" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
       <x:c r="A25" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
       <x:c r="A26" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
       <x:c r="A27" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
       <x:c r="A28" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B30" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
       <x:c r="A31" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
       <x:c r="A32" s="5" t="s">
-        <x:v>244</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B32" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C32" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D32" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E32" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F32" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
       <x:c r="A33" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B33" s="5" t="s">
-        <x:v>235</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C33" s="5" t="s">
-        <x:v>98</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D33" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E33" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F33" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
       <x:c r="A34" s="5" t="s">
-        <x:v>179</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B34" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C34" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D34" s="5"/>
       <x:c r="E34" s="5"/>
       <x:c r="F34" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
       <x:c r="A35" s="5" t="s">
-        <x:v>245</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B35" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C35" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D35" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E35" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F35" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
       <x:c r="A36" s="5" t="s">
-        <x:v>246</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B36" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C36" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D36" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E36" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F36" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
       <x:c r="A37" s="5" t="s">
-        <x:v>241</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B37" s="5" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C37" s="5" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D37" s="5" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E37" s="5" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="C37" s="5" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D37" s="5" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="E37" s="5" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="F37" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
       <x:c r="A38" s="5" t="s">
-        <x:v>242</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B38" s="5" t="s">
-        <x:v>237</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C38" s="5" t="s">
-        <x:v>163</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D38" s="5" t="s">
-        <x:v>159</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E38" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F38" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
       <x:c r="A39" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B39" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C39" s="5" t="s">
-        <x:v>253</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D39" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E39" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F39" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B40" s="5" t="s">
-        <x:v>214</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C40" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D40" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E40" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="F40" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
       <x:c r="A41" s="5" t="s">
-        <x:v>197</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B41" s="5" t="s">
-        <x:v>231</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C41" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D41" s="5"/>
       <x:c r="E41" s="5"/>
       <x:c r="F41" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
       <x:c r="A42" s="5" t="s">
-        <x:v>183</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B42" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C42" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D42" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E42" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F42" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
       <x:c r="A43" s="5" t="s">
-        <x:v>194</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B43" s="5" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C43" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D43" s="5" t="s">
-        <x:v>96</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E43" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F43" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:6">
       <x:c r="A44" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B44" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C44" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D44" s="5"/>
       <x:c r="E44" s="5"/>
       <x:c r="F44" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
       <x:c r="A45" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B45" s="5"/>
       <x:c r="C45" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D45" s="5"/>
       <x:c r="E45" s="5"/>
       <x:c r="F45" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
       <x:c r="A46" s="5" t="s">
-        <x:v>150</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B46" s="5" t="s">
-        <x:v>238</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C46" s="5" t="s">
-        <x:v>217</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D46" s="5" t="s">
-        <x:v>216</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E46" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F46" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:6">
       <x:c r="A47" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B47" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C47" s="5" t="s">
-        <x:v>217</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="D47" s="5" t="s">
-        <x:v>216</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="E47" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F47" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6">
       <x:c r="A48" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B48" s="5" t="s">
-        <x:v>239</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C48" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D48" s="5" t="s">
-        <x:v>218</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E48" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F48" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
       <x:c r="A49" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B49" s="5" t="s">
-        <x:v>219</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C49" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D49" s="5" t="s">
-        <x:v>218</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E49" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F49" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
       <x:c r="A50" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B50" s="5" t="s">
-        <x:v>236</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C50" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D50" s="5"/>
       <x:c r="E50" s="5"/>
       <x:c r="F50" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6">
       <x:c r="A51" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B51" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C51" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D51" s="5"/>
       <x:c r="E51" s="5"/>
       <x:c r="F51" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
       <x:c r="A52" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B52" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C52" s="5" t="s">
-        <x:v>254</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D52" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E52" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F52" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
       <x:c r="A53" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B53" s="5" t="s">
-        <x:v>223</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C53" s="5" t="s">
-        <x:v>254</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D53" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="E53" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="F53" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
       <x:c r="A54" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B54" s="5" t="s">
-        <x:v>152</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C54" s="5" t="s">
-        <x:v>250</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D54" s="5" t="s">
-        <x:v>211</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E54" s="5" t="s">
-        <x:v>212</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F54" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
       <x:c r="A55" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B55" s="5" t="s">
-        <x:v>207</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C55" s="5" t="s">
-        <x:v>250</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D55" s="5" t="s">
-        <x:v>211</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E55" s="5" t="s">
-        <x:v>212</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="F55" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
       <x:c r="A56" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B56" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C56" s="5" t="s">
-        <x:v>229</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D56" s="5" t="s">
-        <x:v>255</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E56" s="5" t="s">
-        <x:v>249</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F56" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6">
       <x:c r="A57" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B57" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C57" s="5" t="s">
-        <x:v>229</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D57" s="5" t="s">
-        <x:v>255</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E57" s="5" t="s">
-        <x:v>249</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F57" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6">
       <x:c r="A58" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B58" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="5" t="s">
-        <x:v>229</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D58" s="5" t="s">
-        <x:v>255</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E58" s="5" t="s">
-        <x:v>249</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="F58" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
       <x:c r="A59" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B59" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C59" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D59" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E59" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F59" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
       <x:c r="A60" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B60" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C60" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D60" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E60" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F60" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
       <x:c r="A61" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B61" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C61" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D61" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E61" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F61" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
       <x:c r="A62" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B62" s="5" t="s">
-        <x:v>206</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C62" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D62" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E62" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F62" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
       <x:c r="A63" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B63" s="5" t="s">
-        <x:v>210</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C63" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D63" s="5" t="s">
-        <x:v>107</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E63" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F63" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
       <x:c r="A64" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B64" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C64" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D64" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E64" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F64" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6">
       <x:c r="A65" s="5" t="s">
-        <x:v>175</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B65" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C65" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D65" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E65" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F65" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
       <x:c r="A66" s="5" t="s">
-        <x:v>172</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B66" s="5" t="s">
-        <x:v>252</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C66" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D66" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E66" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F66" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
       <x:c r="A67" s="5" t="s">
-        <x:v>174</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B67" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C67" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D67" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E67" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F67" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
       <x:c r="A68" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B68" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C68" s="5" t="s">
-        <x:v>248</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D68" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E68" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F68" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
       <x:c r="A69" s="5" t="s">
-        <x:v>173</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B69" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C69" s="5" t="s">
-        <x:v>248</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D69" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="E69" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F69" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:6">
       <x:c r="A70" s="5" t="s">
-        <x:v>171</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B70" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C70" s="5" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D70" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E70" s="5" t="s">
-        <x:v>257</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F70" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6">
       <x:c r="A71" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B71" s="5" t="s">
-        <x:v>224</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C71" s="5" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D71" s="5" t="s">
-        <x:v>256</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="E71" s="5" t="s">
-        <x:v>257</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F71" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
       <x:c r="A72" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B72" s="5" t="s">
-        <x:v>258</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C72" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D72" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E72" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F72" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6">
       <x:c r="A73" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B73" s="5" t="s">
-        <x:v>225</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C73" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D73" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E73" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F73" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6">
       <x:c r="A74" s="5" t="s">
-        <x:v>184</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B74" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C74" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D74" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E74" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F74" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
       <x:c r="A75" s="5" t="s">
-        <x:v>112</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B75" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C75" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D75" s="5" t="s">
-        <x:v>91</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E75" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F75" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
       <x:c r="A76" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B76" s="5" t="s">
-        <x:v>222</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C76" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D76" s="5" t="s">
-        <x:v>260</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E76" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F76" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:6">
       <x:c r="A77" s="5" t="s">
-        <x:v>117</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B77" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C77" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D77" s="5" t="s">
-        <x:v>260</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E77" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F77" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:6">
       <x:c r="A78" s="5" t="s">
-        <x:v>114</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B78" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C78" s="5" t="s">
-        <x:v>89</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D78" s="5" t="s">
-        <x:v>260</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E78" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F78" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6">
       <x:c r="A79" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B79" s="5" t="s">
-        <x:v>209</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C79" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D79" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E79" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F79" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:6">
       <x:c r="A80" s="5" t="s">
-        <x:v>186</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B80" s="5" t="s">
-        <x:v>220</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C80" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D80" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E80" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F80" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:6">
       <x:c r="A81" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="5" t="s">
-        <x:v>228</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C81" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D81" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E81" s="5" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:6">
       <x:c r="A82" s="5" t="s">
-        <x:v>125</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B82" s="5" t="s">
-        <x:v>215</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C82" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D82" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E82" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F82" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:6">
       <x:c r="A83" s="5" t="s">
-        <x:v>129</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C83" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D83" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E83" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F83" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:6">
       <x:c r="A84" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B84" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C84" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D84" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E84" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F84" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:6">
       <x:c r="A85" s="5" t="s">
-        <x:v>119</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B85" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C85" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D85" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E85" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F85" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:6">
       <x:c r="A86" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B86" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C86" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D86" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E86" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F86" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:6">
       <x:c r="A87" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C87" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D87" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E87" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F87" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:6">
       <x:c r="A88" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B88" s="5" t="s">
-        <x:v>208</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C88" s="5" t="s">
-        <x:v>88</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D88" s="5" t="s">
-        <x:v>259</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E88" s="5" t="s">
-        <x:v>213</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F88" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:6">
       <x:c r="A89" s="5" t="s">
-        <x:v>128</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B89" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C89" s="5" t="s">
-        <x:v>166</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D89" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E89" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F89" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:6">
       <x:c r="A90" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B90" s="5" t="s">
-        <x:v>226</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C90" s="5" t="s">
-        <x:v>166</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D90" s="5" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E90" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F90" s="5" t="s">
-        <x:v>155</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:6">
       <x:c r="A91" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B91" s="5" t="s">
-        <x:v>240</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C91" s="5" t="s">
-        <x:v>166</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D91" s="5" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E91" s="5" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="F91" s="5" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:6">
+      <x:c r="A92" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B92" s="6" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C92" s="6" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D92" s="6" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="E92" s="6" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F92" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:6">
+      <x:c r="A93" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B93" s="6" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="C93" s="6" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D93" s="6"/>
+      <x:c r="E93" s="6"/>
+      <x:c r="F93" s="6" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:6">
+      <x:c r="A94" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B94" s="6" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C94" s="6" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D94" s="6" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E94" s="6" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F94" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:6">
+      <x:c r="A95" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B95" s="6" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C95" s="6" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D95" s="6" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E95" s="6" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F95" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:6">
+      <x:c r="A96" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B96" s="6" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C96" s="6" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D96" s="6" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="E96" s="6" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F96" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:6">
+      <x:c r="A97" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B97" s="6" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C97" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D97" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E97" s="6" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F97" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:6">
+      <x:c r="A98" s="6" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B98" s="6">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C98" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D98" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E98" s="6" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F98" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:6">
+      <x:c r="A99" s="6" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B99" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C99" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D99" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E99" s="6" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F99" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:6">
+      <x:c r="A100" s="6" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B100" s="6" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="C100" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D100" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E100" s="6" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F100" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:6">
+      <x:c r="A101" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B101" s="6" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C101" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D101" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E101" s="6" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F101" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:6">
+      <x:c r="A102" s="6" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B102" s="6" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="C102" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D102" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E102" s="6" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F102" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:6">
+      <x:c r="A103" s="6" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B103" s="6" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C103" s="6" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D103" s="6" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E103" s="6" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F103" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:6">
+      <x:c r="A104" s="6" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B104" s="6" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="C104" s="6" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D104" s="6" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="E104" s="6" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="F104" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:6">
+      <x:c r="A105" s="6" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="E91" s="5" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F91" s="5" t="s">
-        <x:v>155</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:1">
-      <x:c r="A92" s="6"/>
-    </x:row>
-    <x:row r="93" spans="1:1">
-      <x:c r="A93" s="6"/>
-    </x:row>
-    <x:row r="94" spans="1:1">
-      <x:c r="A94" s="6"/>
-    </x:row>
-    <x:row r="95" spans="1:1">
-      <x:c r="A95" s="6"/>
-    </x:row>
-    <x:row r="96" spans="1:1">
-      <x:c r="A96" s="6"/>
-    </x:row>
-    <x:row r="97" spans="1:1">
-      <x:c r="A97" s="6"/>
-    </x:row>
-    <x:row r="98" spans="1:1">
-      <x:c r="A98" s="6"/>
-    </x:row>
-    <x:row r="99" spans="1:1">
-      <x:c r="A99" s="6"/>
-    </x:row>
-    <x:row r="100" spans="1:1">
-      <x:c r="A100" s="6"/>
-    </x:row>
-    <x:row r="101" spans="1:1">
-      <x:c r="A101" s="6"/>
-    </x:row>
-    <x:row r="102" spans="1:1">
-      <x:c r="A102" s="6"/>
-    </x:row>
-    <x:row r="103" spans="1:1">
-      <x:c r="A103" s="6"/>
-    </x:row>
-    <x:row r="104" spans="1:1">
-      <x:c r="A104" s="6"/>
-    </x:row>
-    <x:row r="105" spans="1:1">
-      <x:c r="A105" s="6"/>
-    </x:row>
-    <x:row r="106" spans="1:1">
-      <x:c r="A106" s="6"/>
-    </x:row>
-    <x:row r="107" spans="1:1">
-      <x:c r="A107" s="6"/>
-    </x:row>
-    <x:row r="108" spans="1:1">
-      <x:c r="A108" s="6"/>
-    </x:row>
-    <x:row r="109" spans="1:1">
-      <x:c r="A109" s="6"/>
+      <x:c r="B105" s="6" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C105" s="6" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="D105" s="6" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="E105" s="6" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F105" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:6">
+      <x:c r="A106" s="6" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B106" s="6" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C106" s="6" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="D106" s="6" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="E106" s="6" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="F106" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:6">
+      <x:c r="A107" s="6" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B107" s="6" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="C107" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D107" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E107" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F107" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:6">
+      <x:c r="A108" s="6" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B108" s="6" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="C108" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D108" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E108" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F108" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:6">
+      <x:c r="A109" s="6" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B109" s="6" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C109" s="6" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D109" s="6" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="E109" s="6" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="F109" s="6" t="s">
+        <x:v>142</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>